--- a/운동프로그램_10일주기_v19.xlsx
+++ b/운동프로그램_10일주기_v19.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b2bc197408547891/Desktop/운동/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_56CBE09B577CB57806506320C7833877887CCA2D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_56CBE09B577CB57806506320C7833877887CCA2D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1D8F05A-83DF-4046-829E-89604C9450C5}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="883" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4087,6 +4087,10 @@
     <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="177" fontId="51" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -4094,10 +4098,6 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -4489,7 +4489,7 @@
         <v>98</v>
       </c>
       <c r="C4" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>99</v>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="E7" s="9">
         <f>INDEX(증량기록!$C$10:$C$21,$C$4)</f>
-        <v>52.5</v>
+        <v>57.5</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>106</v>
@@ -4553,7 +4553,7 @@
       </c>
       <c r="E8" s="9">
         <f>INDEX(증량기록!$E$10:$E$21,$C$4)</f>
-        <v>57.5</v>
+        <v>62.5</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>108</v>
@@ -4575,7 +4575,7 @@
       </c>
       <c r="E9" s="9">
         <f>INDEX(증량기록!$G$10:$G$21,$C$4)</f>
-        <v>29.25</v>
+        <v>31.5</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>106</v>
@@ -4597,7 +4597,7 @@
       </c>
       <c r="E10" s="9">
         <f>INDEX(증량기록!$I$10:$I$21,$C$4)</f>
-        <v>23.75</v>
+        <v>25</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>111</v>
@@ -5649,16 +5649,16 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1">
-      <c r="A2" s="114" t="s">
+      <c r="A2" s="116" t="s">
         <v>498</v>
       </c>
-      <c r="B2" s="113"/>
-      <c r="C2" s="113"/>
-      <c r="D2" s="113"/>
-      <c r="E2" s="113"/>
-      <c r="F2" s="113"/>
-      <c r="G2" s="113"/>
-      <c r="H2" s="113"/>
+      <c r="B2" s="115"/>
+      <c r="C2" s="115"/>
+      <c r="D2" s="115"/>
+      <c r="E2" s="115"/>
+      <c r="F2" s="115"/>
+      <c r="G2" s="115"/>
+      <c r="H2" s="115"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
@@ -5670,16 +5670,16 @@
       </c>
     </row>
     <row r="4" spans="1:8" ht="39.75" customHeight="1">
-      <c r="A4" s="112" t="s">
+      <c r="A4" s="114" t="s">
         <v>500</v>
       </c>
-      <c r="B4" s="113"/>
-      <c r="C4" s="113"/>
-      <c r="D4" s="113"/>
-      <c r="E4" s="113"/>
-      <c r="F4" s="113"/>
-      <c r="G4" s="113"/>
-      <c r="H4" s="113"/>
+      <c r="B4" s="115"/>
+      <c r="C4" s="115"/>
+      <c r="D4" s="115"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="115"/>
+      <c r="H4" s="115"/>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1">
       <c r="A6" s="44" t="s">
@@ -7685,7 +7685,7 @@
       <c r="F5" s="53" t="s">
         <v>598</v>
       </c>
-      <c r="G5" s="115" t="s">
+      <c r="G5" s="112" t="s">
         <v>599</v>
       </c>
       <c r="H5" s="56">
@@ -7728,7 +7728,7 @@
       <c r="F6" s="53" t="s">
         <v>600</v>
       </c>
-      <c r="G6" s="116"/>
+      <c r="G6" s="113"/>
       <c r="J6" s="55">
         <f t="shared" ca="1" si="2"/>
         <v>12.6</v>
@@ -7761,7 +7761,7 @@
       <c r="F7" s="53" t="s">
         <v>601</v>
       </c>
-      <c r="G7" s="115" t="s">
+      <c r="G7" s="112" t="s">
         <v>602</v>
       </c>
       <c r="H7" s="56">
@@ -7800,7 +7800,7 @@
       <c r="F8" s="53" t="s">
         <v>603</v>
       </c>
-      <c r="G8" s="116"/>
+      <c r="G8" s="113"/>
       <c r="J8" s="55">
         <f t="shared" ca="1" si="2"/>
         <v>3.9</v>
@@ -7833,7 +7833,7 @@
       <c r="F9" s="53" t="s">
         <v>604</v>
       </c>
-      <c r="G9" s="116"/>
+      <c r="G9" s="113"/>
       <c r="J9" s="55">
         <f t="shared" ca="1" si="2"/>
         <v>9.8000000000000007</v>
@@ -7866,7 +7866,7 @@
       <c r="F10" s="53" t="s">
         <v>605</v>
       </c>
-      <c r="G10" s="116"/>
+      <c r="G10" s="113"/>
       <c r="J10" s="55">
         <f t="shared" ca="1" si="2"/>
         <v>16.100000000000001</v>
@@ -8104,7 +8104,7 @@
       <c r="F17" s="53" t="s">
         <v>612</v>
       </c>
-      <c r="G17" s="115" t="s">
+      <c r="G17" s="112" t="s">
         <v>337</v>
       </c>
       <c r="H17" s="56">
@@ -8143,7 +8143,7 @@
       <c r="F18" s="53" t="s">
         <v>613</v>
       </c>
-      <c r="G18" s="116"/>
+      <c r="G18" s="113"/>
       <c r="J18" s="55">
         <f t="shared" ca="1" si="2"/>
         <v>9.1</v>
@@ -8900,7 +8900,9 @@
       <c r="A14" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="B14" s="4"/>
+      <c r="B14" s="84">
+        <v>46265</v>
+      </c>
       <c r="C14" s="16">
         <f t="shared" si="0"/>
         <v>57.5</v>
@@ -9846,7 +9848,7 @@
       </c>
       <c r="D5" s="75">
         <f>시작중량_설정!$E$7</f>
-        <v>52.5</v>
+        <v>57.5</v>
       </c>
       <c r="E5" s="67">
         <v>5</v>
@@ -9886,7 +9888,7 @@
       </c>
       <c r="D6" s="75">
         <f>시작중량_설정!$E$10</f>
-        <v>23.75</v>
+        <v>25</v>
       </c>
       <c r="E6" s="67">
         <v>3</v>
@@ -10343,7 +10345,7 @@
       </c>
       <c r="D5" s="78">
         <f>시작중량_설정!$E$8</f>
-        <v>57.5</v>
+        <v>62.5</v>
       </c>
       <c r="E5" s="67">
         <v>1</v>
@@ -11475,7 +11477,7 @@
       </c>
       <c r="D5" s="75">
         <f>시작중량_설정!$E$9</f>
-        <v>29.25</v>
+        <v>31.5</v>
       </c>
       <c r="E5" s="67">
         <v>5</v>
@@ -15356,7 +15358,7 @@
     <row r="10" spans="1:3" ht="15" customHeight="1">
       <c r="A10" s="37">
         <f>시작중량_설정!$E$9</f>
-        <v>29.25</v>
+        <v>31.5</v>
       </c>
       <c r="B10" s="27">
         <v>5</v>
@@ -15451,7 +15453,7 @@
       </c>
       <c r="D20" s="41">
         <f>시작중량_설정!$E$9</f>
-        <v>29.25</v>
+        <v>31.5</v>
       </c>
       <c r="E20" s="40">
         <v>5</v>
@@ -15745,7 +15747,7 @@
     <row r="6" spans="1:14" ht="15" customHeight="1">
       <c r="A6" s="20">
         <f>MAX(20,MROUND(시작중량_설정!$E$7*0.4,2.5))</f>
-        <v>20</v>
+        <v>22.5</v>
       </c>
       <c r="B6" s="20">
         <v>5</v>
@@ -15757,7 +15759,7 @@
     <row r="7" spans="1:14" ht="15" customHeight="1">
       <c r="A7" s="20">
         <f>IF(MAX(20,MROUND(시작중량_설정!$E$7*0.6,2.5))&lt;=MAX(20,MROUND(시작중량_설정!$E$7*0.4,2.5)),"생략",MAX(20,MROUND(시작중량_설정!$E$7*0.6,2.5)))</f>
-        <v>32.5</v>
+        <v>35</v>
       </c>
       <c r="B7" s="20">
         <v>5</v>
@@ -15769,7 +15771,7 @@
     <row r="8" spans="1:14" ht="15" customHeight="1">
       <c r="A8" s="20">
         <f>IF(MAX(20,MROUND(시작중량_설정!$E$7*0.75,2.5))&lt;=MAX(20,MROUND(시작중량_설정!$E$7*0.6,2.5)),"생략",MAX(20,MROUND(시작중량_설정!$E$7*0.75,2.5)))</f>
-        <v>40</v>
+        <v>42.5</v>
       </c>
       <c r="B8" s="20">
         <v>3</v>
@@ -15781,7 +15783,7 @@
     <row r="9" spans="1:14" ht="15" customHeight="1">
       <c r="A9" s="20">
         <f>IF(MAX(20,MROUND(시작중량_설정!$E$7*0.9,2.5))&lt;=MAX(20,MROUND(시작중량_설정!$E$7*0.75,2.5)),"생략",MAX(20,MROUND(시작중량_설정!$E$7*0.9,2.5)))</f>
-        <v>47.5</v>
+        <v>52.5</v>
       </c>
       <c r="B9" s="20">
         <v>2</v>
@@ -15793,7 +15795,7 @@
     <row r="10" spans="1:14" ht="15" customHeight="1">
       <c r="A10" s="37">
         <f>시작중량_설정!$E$7</f>
-        <v>52.5</v>
+        <v>57.5</v>
       </c>
       <c r="B10" s="27">
         <v>5</v>
@@ -15868,7 +15870,7 @@
       </c>
       <c r="D15" s="41">
         <f>시작중량_설정!$E$7</f>
-        <v>52.5</v>
+        <v>57.5</v>
       </c>
       <c r="E15" s="40">
         <v>5</v>
@@ -17334,7 +17336,7 @@
     <row r="10" spans="1:3" ht="15" customHeight="1">
       <c r="A10" s="37">
         <f>시작중량_설정!$E$10</f>
-        <v>23.75</v>
+        <v>25</v>
       </c>
       <c r="B10" s="27">
         <v>5</v>
@@ -17429,7 +17431,7 @@
       </c>
       <c r="D20" s="41">
         <f>시작중량_설정!$E$10</f>
-        <v>23.75</v>
+        <v>25</v>
       </c>
       <c r="E20" s="40">
         <v>3</v>
@@ -17851,7 +17853,7 @@
     <row r="6" spans="1:14" ht="15" customHeight="1">
       <c r="A6" s="20">
         <f>MAX(20,MROUND(시작중량_설정!$E$8*0.4,2.5))</f>
-        <v>22.5</v>
+        <v>25</v>
       </c>
       <c r="B6" s="20">
         <v>5</v>
@@ -17863,7 +17865,7 @@
     <row r="7" spans="1:14" ht="15" customHeight="1">
       <c r="A7" s="20">
         <f>IF(MAX(20,MROUND(시작중량_설정!$E$8*0.6,2.5))&lt;=MAX(20,MROUND(시작중량_설정!$E$8*0.4,2.5)),"생략",MAX(20,MROUND(시작중량_설정!$E$8*0.6,2.5)))</f>
-        <v>35</v>
+        <v>37.5</v>
       </c>
       <c r="B7" s="20">
         <v>5</v>
@@ -17875,7 +17877,7 @@
     <row r="8" spans="1:14" ht="15" customHeight="1">
       <c r="A8" s="20">
         <f>IF(MAX(20,MROUND(시작중량_설정!$E$8*0.75,2.5))&lt;=MAX(20,MROUND(시작중량_설정!$E$8*0.6,2.5)),"생략",MAX(20,MROUND(시작중량_설정!$E$8*0.75,2.5)))</f>
-        <v>42.5</v>
+        <v>47.5</v>
       </c>
       <c r="B8" s="20">
         <v>3</v>
@@ -17887,7 +17889,7 @@
     <row r="9" spans="1:14" ht="15" customHeight="1">
       <c r="A9" s="20">
         <f>IF(MAX(20,MROUND(시작중량_설정!$E$8*0.9,2.5))&lt;=MAX(20,MROUND(시작중량_설정!$E$8*0.75,2.5)),"생략",MAX(20,MROUND(시작중량_설정!$E$8*0.9,2.5)))</f>
-        <v>52.5</v>
+        <v>57.5</v>
       </c>
       <c r="B9" s="20">
         <v>2</v>
@@ -17899,7 +17901,7 @@
     <row r="10" spans="1:14" ht="15" customHeight="1">
       <c r="A10" s="37">
         <f>시작중량_설정!$E$8</f>
-        <v>57.5</v>
+        <v>62.5</v>
       </c>
       <c r="B10" s="27">
         <v>5</v>
@@ -17974,7 +17976,7 @@
       </c>
       <c r="D15" s="41">
         <f>시작중량_설정!$E$8</f>
-        <v>57.5</v>
+        <v>62.5</v>
       </c>
       <c r="E15" s="40">
         <v>1</v>
@@ -18014,7 +18016,7 @@
       </c>
       <c r="D16" s="41">
         <f>시작중량_설정!$E$8-증량기록!$C$5</f>
-        <v>52.5</v>
+        <v>57.5</v>
       </c>
       <c r="E16" s="40">
         <v>2</v>

--- a/운동프로그램_10일주기_v19.xlsx
+++ b/운동프로그램_10일주기_v19.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b2bc197408547891/Desktop/운동/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="247" documentId="11_56CBE09B577CB57806506320C7833877887CCA2D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08769037-AA74-4934-AC98-BC628FB9C1B8}"/>
+  <xr:revisionPtr revIDLastSave="287" documentId="11_56CBE09B577CB57806506320C7833877887CCA2D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB69CF8B-16AB-422C-B771-8A9ED9E2056F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="883" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2170" uniqueCount="1119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2173" uniqueCount="1122">
   <si>
     <t>9일차 — 어깨·팔 B</t>
   </si>
@@ -1281,9 +1281,6 @@
   </si>
   <si>
     <t>20</t>
-  </si>
-  <si>
-    <t>[2026-09-04 신설] 승모 하부는 실질 4.5로 가장 크게 모자랐다. 7일차에 같은 종목이 3세트 있었지만 사이클당 1회뿐이었고, 여기와 9일차를 더해 3회로 만들었다. 견갑 상방회전 — 팔을 머리 위에 둔 채 으쓱한다.</t>
   </si>
   <si>
     <t>오버헤드 케이블 슈러그 / 프론 Y 레이즈</t>
@@ -3347,10 +3344,6 @@
     <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
-    <t>[2026-09-05 9일차 → 4일차 이동] 종아리 1·4·6·8일차. [2026-09-04 신설] 무릎 굽힌 상태 — 가자미근. 1일차 스탠딩(비복근)과 각도를 나눈다. 8일차에 같은 종목이 4세트 있고 여기 2세트를 더해 종아리를 주당 10으로 올린다.</t>
-    <phoneticPr fontId="32" type="noConversion"/>
-  </si>
-  <si>
     <t>[2026-09-05 4일차 → 7일차 이동 — 사용자 요청] 흉근 중하부 고립. 헤머 체스트·인클라인 머신 두 프레스 뒤 마무리 자리다. 위에서 아래로 내리는 궤적이라 하부 섬유 비중이 크고, 케이블이라 수축 지점에서도 장력이 유지된다. 흉근 합산이 천장(20)을 넘어 있어 세트 질이 떨어지면 먼저 빼는 후보가 이 3세트다. [이력] 이 행은 v18 전 삼두 종목 자리였고, 2026-09-04 2일차 → 4일차, 오늘 7일차로 왔다.</t>
     <phoneticPr fontId="32" type="noConversion"/>
   </si>
@@ -3375,10 +3368,6 @@
     <t>· 4일차 디클라인 케이블 플라이 3세트가 인클라인 머신 뒤 6번으로 왔다 — 사용자 요청. 흉근 9세트(헤머 3 · 인클라인 머신 3 · 디클라인 3). 27세트 · 약 67분.</t>
   </si>
   <si>
-    <t>삼각근(측면·후면) · 흉근(인클라인 스미스 · 펙덱) · 이두 · 전완 · 종아리</t>
-    <phoneticPr fontId="32" type="noConversion"/>
-  </si>
-  <si>
     <t>삼각근(측면·후면·전면) · 승모(하부) · 흉근(상부 플라이) · 삼두 · 이두 · 전완 · 내전근 · 중둔근</t>
     <phoneticPr fontId="32" type="noConversion"/>
   </si>
@@ -3402,18 +3391,10 @@
     <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
-    <t>측면·후면 삼각근 + 흉근(인클라인 스미스 · 펙덱) + 이두 · 전완 + 종아리. 약 70분. 4-1-4-1 전환으로 신설 — 옛 8일차 어깨 세션의 절반과 1·2일차의 팔이 여기로 왔다. 거울 슬롯은 9일차 어깨·팔 B. [2026-09-05] 이너·아우터 타이·리스트 컬은 9일차로, 디클라인 플라이는 7일차로 갔고, 9일차의 리버스 리스트 컬·리버스컬·시티드 카프와 6일차 스탠딩 카프가 왔다.</t>
-    <phoneticPr fontId="32" type="noConversion"/>
-  </si>
-  <si>
     <t>측면 · 후면 · 전면 삼각근 + 하부 승모 + 흉근 상부 플라이 + 삼두 · 이두 · 전완 + 내전근·중둔근. 약 70분. 옛 8일차 어깨 세션의 절반 — 나머지 절반은 4일차 어깨·팔 A. 8일차 데드 다음 날이라 척추 부하 0은 그대로다. [2026-09-05] 인클라인 덤벨 플라이 3세트 추가(5번). 이너·아우터 타이·리스트 컬(손등 위)이 4일차에서 왔고 리버스 리스트 컬·리버스컬·시티드 카프는 4일차로, 케이블 힙 외전은 6일차로 갔다.</t>
     <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
-    <t>로우 · 견갑골 후인 · 이두 · 전완. 1일차 당기기 A(수직)와 각도를 나눈다. [2026-09-05] 스탠딩 카프는 4일차로, 중량 크런치는 7일차로 갔고 9일차 케이블 힙 외전이 왔다. 약 72분.</t>
-    <phoneticPr fontId="32" type="noConversion"/>
-  </si>
-  <si>
     <t>오버헤드 프레싱 · 흉근 상부 · 어깨 측면/후면. 벤치(2일차)와 5일 간격이라 무게가 온전히 나온다. [2026-09-05] 4일차 디클라인 케이블 플라이 3세트가 왔다 — 흉근 9세트(헤머 · 인클라인 머신 · 디클라인). 6일차 중량 크런치 3세트도 마지막에 왔다 — 약 72분.</t>
     <phoneticPr fontId="32" type="noConversion"/>
   </si>
@@ -3430,15 +3411,44 @@
     <t>· 케이블 힙 외전은 6일차로 갔다 — 중둔근을 3·6·9일차로 펴고 이 날을 70분으로. 36세트.</t>
   </si>
   <si>
-    <t>광배 · 능형근 · 승모 · 이두 · 기립근 · 중둔근</t>
-    <phoneticPr fontId="32" type="noConversion"/>
-  </si>
-  <si>
     <t>삼각근 · 흉근(상부 · 디클라인 플라이) · 승모(하부) · 복부</t>
     <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>· [2026-09-05] 세 자리 회전 — 사용자 합의: 9일차 케이블 힙 외전 → 6일차(카프 자리, 백 익스텐션 앞), 6일차 스탠딩 카프 → 4일차, 6일차 중량 크런치 → 7일차 마지막. 중둔근 3·6·9(3/3/4일) · 종아리 1·4·8(3/4/3일) · 복부 1·3·7(2/4/4일). 세션이 전부 68~73분 — 4일차 35 약 70 · 6일차 31 약 72 · 7일차 30 약 72 · 9일차 36 약 70. 데드 전날 크런치는 마지막 종목으로 가볍게, 셋업에서 배 힘이 덜 들어가면 6일차로 되돌린다.</t>
+  </si>
+  <si>
+    <t>[2026-09-05 6일차 → 4일차 이동] 6·7일차 이틀 연속이던 승모 하부를 4·7·9일차(3/2/5일)로 폈다. 스미스에서 하므로 바로 뒤 인클라인 스미스와 같은 기구 — 벤치만 넣으면 된다. [2026-09-04 신설] 승모 하부는 실질 4.5로 가장 크게 모자랐다. 7일차에 같은 종목이 3세트 있었지만 사이클당 1회뿐이었고, 여기와 9일차를 더해 3회로 만들었다. 견갑 상방회전 — 팔을 머리 위에 둔 채 으쓱한다.</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>[2026-09-05 4일차 → 6일차 이동] 오버헤드 슈러그에 자리를 내주고 왔다. 종아리 1·4·6·8일차(3/2/2/3일) — 4일차 스탠딩(비복근)과 6·8일차 시티드(가자미근)는 다른 근육이라 이틀 간격이 겹치지 않는다. [2026-09-05 9일차 → 4일차 이동] 종아리 1·4·6·8일차. [2026-09-04 신설] 무릎 굽힌 상태 — 가자미근. 1일차 스탠딩(비복근)과 각도를 나눈다. 8일차에 같은 종목이 4세트 있고 여기 2세트를 더해 종아리를 주당 10으로 올린다.</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>측면·후면 삼각근 + 승모 하부 + 흉근(인클라인 스미스 · 펙덱) + 이두 · 전완 + 종아리. 약 71분. 4-1-4-1 전환으로 신설 — 옛 8일차 어깨 세션의 절반과 1·2일차의 팔이 여기로 왔다. 거울 슬롯은 9일차 어깨·팔 B. [2026-09-05] 이너·아우터 타이·리스트 컬은 9일차로, 디클라인 플라이는 7일차로, 시티드 카프는 6일차로 갔고, 9일차의 리버스 리스트 컬·리버스컬과 6일차 스탠딩 카프·오버헤드 슈러그가 왔다.</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>로우 · 견갑골 후인 · 이두 · 전완. 1일차 당기기 A(수직)와 각도를 나눈다. [2026-09-05] 스탠딩 카프는 4일차로, 중량 크런치는 7일차로 갔고 9일차 케이블 힙 외전이 왔다. 약 72분. 오버헤드 슈러그는 4일차로 가고 4일차 시티드 카프 2세트가 왔다 — 약 71분.</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>· 6일차 오버헤드 슈러그 3세트가 5번(인클라인 스미스 앞, 같은 스미스 머신)으로 왔고 시티드 카프 2세트는 6일차로 갔다. 승모 하부 4·7·9일차. 36세트 · 약 71분.</t>
+  </si>
+  <si>
+    <t>· 오버헤드 슈러그 → 4일차, 4일차 시티드 카프 2세트가 8번(힙 외전 앞)으로 왔다. 6·7일차 이틀 연속이던 승모 하부가 풀렸다. 30세트 · 약 71분.</t>
+  </si>
+  <si>
+    <t>삼각근(측면·후면) · 승모(하부) · 흉근(인클라인 스미스 · 펙덱) · 이두 · 전완 · 종아리</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>광배 · 능형근 · 승모(중부·상부) · 이두 · 기립근 · 중둔근 · 종아리</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>· [2026-09-05] 6일차 오버헤드 슈러그 ↔ 4일차 시티드 카프 맞교환 — 마지막 남은 이틀 연속(승모 하부 6·7일차)을 풀었다. 승모 하부 4·7·9(3/2/5일), 종아리 1·4·6·8(3/2/2/3일 — 4일차 비복근·6·8일차 가자미근). 4일차 36세트 약 71분 · 6일차 30세트 약 71분. 이제 이틀 연속으로 맞는 부위가 없다.</t>
   </si>
 </sst>
 </file>
@@ -4182,7 +4192,7 @@
     <cellStyle name="표준" xfId="0" builtinId="0"/>
     <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
   </cellStyles>
-  <dxfs count="14">
+  <dxfs count="13">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -4205,16 +4215,6 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF95A5A6"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF2F2F2"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5146,7 +5146,7 @@
     </row>
     <row r="2" spans="1:14" ht="16.5" customHeight="1">
       <c r="A2" s="18" t="s">
-        <v>1109</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="30" customHeight="1">
@@ -5360,7 +5360,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="81" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="C10" s="20" t="s">
         <v>301</v>
@@ -5386,7 +5386,7 @@
       </c>
       <c r="J10" s="21"/>
       <c r="K10" s="21" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="L10" s="21" t="s">
         <v>308</v>
@@ -5499,7 +5499,7 @@
       </c>
       <c r="J13" s="21"/>
       <c r="K13" s="21" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="L13" s="21" t="s">
         <v>373</v>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="J14" s="21"/>
       <c r="K14" s="21" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="L14" s="21" t="s">
         <v>375</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="J15" s="21"/>
       <c r="K15" s="21" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="L15" s="21" t="s">
         <v>376</v>
@@ -5732,22 +5732,22 @@
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="31" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>1115</v>
+        <v>1110</v>
       </c>
     </row>
   </sheetData>
@@ -5777,12 +5777,12 @@
   <sheetData>
     <row r="1" spans="1:8" ht="19.5" customHeight="1">
       <c r="A1" s="17" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1">
       <c r="A2" s="114" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B2" s="113"/>
       <c r="C2" s="113"/>
@@ -5794,7 +5794,7 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F3">
         <f ca="1">COUNTIF($E$7:$E$80,"?")</f>
@@ -5803,7 +5803,7 @@
     </row>
     <row r="4" spans="1:8" ht="39.75" customHeight="1">
       <c r="A4" s="112" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B4" s="113"/>
       <c r="C4" s="113"/>
@@ -5815,33 +5815,33 @@
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1">
       <c r="A6" s="44" t="s">
+        <v>475</v>
+      </c>
+      <c r="B6" s="44" t="s">
         <v>476</v>
       </c>
-      <c r="B6" s="44" t="s">
+      <c r="C6" s="44" t="s">
         <v>477</v>
       </c>
-      <c r="C6" s="44" t="s">
+      <c r="D6" s="44" t="s">
         <v>478</v>
       </c>
-      <c r="D6" s="44" t="s">
+      <c r="E6" s="44" t="s">
         <v>479</v>
       </c>
-      <c r="E6" s="44" t="s">
+      <c r="F6" s="44" t="s">
         <v>480</v>
       </c>
-      <c r="F6" s="44" t="s">
+      <c r="G6" s="44" t="s">
         <v>481</v>
       </c>
-      <c r="G6" s="44" t="s">
+      <c r="H6" s="44" t="s">
         <v>482</v>
-      </c>
-      <c r="H6" s="44" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15" customHeight="1">
       <c r="A7" s="45" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B7" s="45" t="s">
         <v>237</v>
@@ -5861,15 +5861,15 @@
         <v>2</v>
       </c>
       <c r="G7" s="49" t="s">
+        <v>484</v>
+      </c>
+      <c r="H7" s="50" t="s">
         <v>485</v>
-      </c>
-      <c r="H7" s="50" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1">
       <c r="A8" s="45" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B8" s="45" t="s">
         <v>243</v>
@@ -5889,15 +5889,15 @@
         <v>0.8</v>
       </c>
       <c r="G8" s="49" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H8" s="50" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15" customHeight="1">
       <c r="A9" s="45" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B9" s="45" t="s">
         <v>387</v>
@@ -5917,15 +5917,15 @@
         <v>1</v>
       </c>
       <c r="G9" s="49" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H9" s="50" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15" customHeight="1">
       <c r="A10" s="45" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B10" s="45" t="s">
         <v>391</v>
@@ -5945,15 +5945,15 @@
         <v>1.6500000000000001</v>
       </c>
       <c r="G10" s="49" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H10" s="50" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1">
       <c r="A11" s="45" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B11" s="45" t="s">
         <v>289</v>
@@ -5973,15 +5973,15 @@
         <v>1.6500000000000001</v>
       </c>
       <c r="G11" s="49" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H11" s="50" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1">
       <c r="A12" s="45" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B12" s="45" t="s">
         <v>296</v>
@@ -6001,18 +6001,18 @@
         <v>2</v>
       </c>
       <c r="G12" s="49" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H12" s="50" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="15" customHeight="1">
       <c r="A13" s="45" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B13" s="45" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C13" s="45" t="s">
         <v>39</v>
@@ -6029,18 +6029,18 @@
         <v>0.99</v>
       </c>
       <c r="G13" s="49" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H13" s="50" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1">
       <c r="A14" s="45" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B14" s="45" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C14" s="45" t="s">
         <v>39</v>
@@ -6057,15 +6057,15 @@
         <v>1.5</v>
       </c>
       <c r="G14" s="49" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H14" s="50" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="15" customHeight="1">
       <c r="A15" s="45" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="B15" s="45" t="s">
         <v>300</v>
@@ -6085,15 +6085,15 @@
         <v>1.5</v>
       </c>
       <c r="G15" s="49" t="s">
+        <v>496</v>
+      </c>
+      <c r="H15" s="50" t="s">
         <v>497</v>
-      </c>
-      <c r="H15" s="50" t="s">
-        <v>498</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="15" customHeight="1">
       <c r="A16" s="45" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B16" s="45" t="s">
         <v>43</v>
@@ -6113,15 +6113,15 @@
         <v>1.32</v>
       </c>
       <c r="G16" s="49" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H16" s="50" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="15" customHeight="1">
       <c r="A17" s="45" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B17" s="45" t="s">
         <v>400</v>
@@ -6141,15 +6141,15 @@
         <v>1.32</v>
       </c>
       <c r="G17" s="49" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H17" s="50" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="15" customHeight="1">
       <c r="A18" s="45" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B18" s="45" t="s">
         <v>403</v>
@@ -6169,15 +6169,15 @@
         <v>0</v>
       </c>
       <c r="G18" s="49" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H18" s="50" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="15" customHeight="1">
       <c r="A19" s="45" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B19" s="45" t="s">
         <v>289</v>
@@ -6197,15 +6197,15 @@
         <v>1.6500000000000001</v>
       </c>
       <c r="G19" s="49" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H19" s="50" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="15" customHeight="1">
       <c r="A20" s="45" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="B20" s="45" t="s">
         <v>300</v>
@@ -6225,18 +6225,18 @@
         <v>1.5</v>
       </c>
       <c r="G20" s="49" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H20" s="50" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="15" customHeight="1">
       <c r="A21" s="45" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B21" s="45" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C21" s="45" t="s">
         <v>27</v>
@@ -6253,18 +6253,18 @@
         <v>1.5</v>
       </c>
       <c r="G21" s="49" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H21" s="50" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1">
       <c r="A22" s="45" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B22" s="45" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C22" s="45" t="s">
         <v>18</v>
@@ -6281,15 +6281,15 @@
         <v>0.99</v>
       </c>
       <c r="G22" s="49" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H22" s="50" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1">
       <c r="A23" s="45" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B23" s="45" t="s">
         <v>26</v>
@@ -6309,15 +6309,15 @@
         <v>0.99</v>
       </c>
       <c r="G23" s="52" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H23" s="50" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="15" customHeight="1">
       <c r="A24" s="45" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B24" s="45" t="s">
         <v>26</v>
@@ -6337,15 +6337,15 @@
         <v>0.99</v>
       </c>
       <c r="G24" s="52" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H24" s="50" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="15" customHeight="1">
       <c r="A25" s="45" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B25" s="45" t="s">
         <v>253</v>
@@ -6365,15 +6365,15 @@
         <v>1.5</v>
       </c>
       <c r="G25" s="49" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H25" s="50" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="15" customHeight="1">
       <c r="A26" s="45" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B26" s="45" t="s">
         <v>33</v>
@@ -6393,15 +6393,15 @@
         <v>1.5</v>
       </c>
       <c r="G26" s="52" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H26" s="50" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="15" customHeight="1">
       <c r="A27" s="45" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B27" s="45" t="s">
         <v>33</v>
@@ -6421,15 +6421,15 @@
         <v>1.5</v>
       </c>
       <c r="G27" s="49" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H27" s="51" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="15" customHeight="1">
       <c r="A28" s="45" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B28" s="45" t="s">
         <v>387</v>
@@ -6449,15 +6449,15 @@
         <v>2.5</v>
       </c>
       <c r="G28" s="49" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H28" s="50" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="15" customHeight="1">
       <c r="A29" s="45" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B29" s="45" t="s">
         <v>391</v>
@@ -6477,15 +6477,15 @@
         <v>2.5</v>
       </c>
       <c r="G29" s="49" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H29" s="50" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="15" customHeight="1">
       <c r="A30" s="45" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B30" s="45" t="s">
         <v>355</v>
@@ -6505,18 +6505,18 @@
         <v>0</v>
       </c>
       <c r="G30" s="49" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H30" s="50" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="15" customHeight="1">
       <c r="A31" s="45" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B31" s="45" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C31" s="45" t="s">
         <v>333</v>
@@ -6533,18 +6533,18 @@
         <v>0.8</v>
       </c>
       <c r="G31" s="49" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H31" s="50" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="15" customHeight="1">
       <c r="A32" s="45" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B32" s="45" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C32" s="45" t="s">
         <v>333</v>
@@ -6561,15 +6561,15 @@
         <v>0.33</v>
       </c>
       <c r="G32" s="49" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H32" s="50" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="15" customHeight="1">
       <c r="A33" s="45" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B33" s="45" t="s">
         <v>272</v>
@@ -6589,15 +6589,15 @@
         <v>1.5</v>
       </c>
       <c r="G33" s="49" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H33" s="50" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="15" customHeight="1">
       <c r="A34" s="45" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B34" s="45" t="s">
         <v>317</v>
@@ -6617,15 +6617,15 @@
         <v>2.5</v>
       </c>
       <c r="G34" s="49" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H34" s="50" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="15" customHeight="1">
       <c r="A35" s="45" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B35" s="45" t="s">
         <v>323</v>
@@ -6645,18 +6645,18 @@
         <v>0.99</v>
       </c>
       <c r="G35" s="49" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H35" s="50" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="15" customHeight="1">
       <c r="A36" s="45" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B36" s="45" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C36" s="45" t="s">
         <v>324</v>
@@ -6673,18 +6673,18 @@
         <v>0.5</v>
       </c>
       <c r="G36" s="49" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H36" s="50" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="15" customHeight="1">
       <c r="A37" s="45" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B37" s="45" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C37" s="45" t="s">
         <v>324</v>
@@ -6701,15 +6701,15 @@
         <v>1.5</v>
       </c>
       <c r="G37" s="49" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H37" s="50" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="15" customHeight="1">
       <c r="A38" s="45" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B38" s="45" t="s">
         <v>272</v>
@@ -6729,15 +6729,15 @@
         <v>1.5</v>
       </c>
       <c r="G38" s="49" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H38" s="50" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="15" customHeight="1">
       <c r="A39" s="45" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B39" s="45" t="s">
         <v>317</v>
@@ -6757,15 +6757,15 @@
         <v>0</v>
       </c>
       <c r="G39" s="49" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H39" s="50" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="15" customHeight="1">
       <c r="A40" s="45" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B40" s="45" t="s">
         <v>403</v>
@@ -6785,18 +6785,18 @@
         <v>0</v>
       </c>
       <c r="G40" s="49" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H40" s="50" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="15" customHeight="1">
       <c r="A41" s="45" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B41" s="45" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C41" s="45" t="s">
         <v>273</v>
@@ -6813,15 +6813,15 @@
         <v>1.5</v>
       </c>
       <c r="G41" s="49" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H41" s="51" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="15" customHeight="1">
       <c r="A42" s="45" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B42" s="45" t="s">
         <v>327</v>
@@ -6841,15 +6841,15 @@
         <v>1.5</v>
       </c>
       <c r="G42" s="49" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H42" s="50" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="15" customHeight="1">
       <c r="A43" s="45" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B43" s="45" t="s">
         <v>327</v>
@@ -6869,18 +6869,18 @@
         <v>0.99</v>
       </c>
       <c r="G43" s="49" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H43" s="50" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="15" customHeight="1">
       <c r="A44" s="45" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B44" s="45" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C44" s="45" t="s">
         <v>238</v>
@@ -6897,15 +6897,15 @@
         <v>0</v>
       </c>
       <c r="G44" s="52" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H44" s="50" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="15" customHeight="1">
       <c r="A45" s="45" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B45" s="45" t="s">
         <v>317</v>
@@ -6925,15 +6925,15 @@
         <v>1.6500000000000001</v>
       </c>
       <c r="G45" s="52" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H45" s="50" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="15" customHeight="1">
       <c r="A46" s="45" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B46" s="45" t="s">
         <v>323</v>
@@ -6953,15 +6953,15 @@
         <v>0.99</v>
       </c>
       <c r="G46" s="52" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H46" s="50" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="15" customHeight="1">
       <c r="A47" s="45" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B47" s="45" t="s">
         <v>327</v>
@@ -6981,15 +6981,15 @@
         <v>0.99</v>
       </c>
       <c r="G47" s="52" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H47" s="50" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="15" customHeight="1">
       <c r="A48" s="45" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B48" s="45" t="s">
         <v>289</v>
@@ -7009,18 +7009,18 @@
         <v>0</v>
       </c>
       <c r="G48" s="52" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H48" s="50" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="15" customHeight="1">
       <c r="A49" s="45" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B49" s="45" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C49" s="45" t="s">
         <v>290</v>
@@ -7037,15 +7037,15 @@
         <v>0</v>
       </c>
       <c r="G49" s="52" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H49" s="50" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="15" customHeight="1">
       <c r="A50" s="45" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B50" s="45" t="s">
         <v>387</v>
@@ -7065,18 +7065,18 @@
         <v>0</v>
       </c>
       <c r="G50" s="52" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H50" s="50" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="15" customHeight="1">
       <c r="A51" s="45" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B51" s="45" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C51" s="45" t="s">
         <v>352</v>
@@ -7093,18 +7093,18 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="G51" s="52" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H51" s="50" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="15" customHeight="1">
       <c r="A52" s="45" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B52" s="45" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C52" s="45" t="s">
         <v>352</v>
@@ -7121,15 +7121,15 @@
         <v>0</v>
       </c>
       <c r="G52" s="52" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H52" s="50" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="15" customHeight="1">
       <c r="A53" s="45" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B53" s="45" t="s">
         <v>237</v>
@@ -7149,15 +7149,15 @@
         <v>0.8</v>
       </c>
       <c r="G53" s="52" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H53" s="50" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="15" customHeight="1">
       <c r="A54" s="45" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B54" s="45" t="s">
         <v>387</v>
@@ -7177,15 +7177,15 @@
         <v>1</v>
       </c>
       <c r="G54" s="52" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H54" s="50" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="15" customHeight="1">
       <c r="A55" s="45" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B55" s="45" t="s">
         <v>312</v>
@@ -7205,15 +7205,15 @@
         <v>1.6500000000000001</v>
       </c>
       <c r="G55" s="52" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H55" s="50" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="15" customHeight="1">
       <c r="A56" s="45" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B56" s="45" t="s">
         <v>323</v>
@@ -7233,15 +7233,15 @@
         <v>0.99</v>
       </c>
       <c r="G56" s="52" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H56" s="50" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="15" customHeight="1">
       <c r="A57" s="45" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B57" s="45" t="s">
         <v>323</v>
@@ -7261,15 +7261,15 @@
         <v>0.99</v>
       </c>
       <c r="G57" s="52" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H57" s="50" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="15" customHeight="1">
       <c r="A58" s="45" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B58" s="45" t="s">
         <v>26</v>
@@ -7289,15 +7289,15 @@
         <v>1.5</v>
       </c>
       <c r="G58" s="52" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H58" s="50" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="15" customHeight="1">
       <c r="A59" s="45" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B59" s="45" t="s">
         <v>26</v>
@@ -7317,18 +7317,18 @@
         <v>1.5</v>
       </c>
       <c r="G59" s="52" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H59" s="50" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="15" customHeight="1">
       <c r="A60" s="45" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B60" s="45" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C60" s="45" t="s">
         <v>39</v>
@@ -7345,15 +7345,15 @@
         <v>1.5</v>
       </c>
       <c r="G60" s="52" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H60" s="50" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="15" customHeight="1">
       <c r="A61" s="45" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B61" s="45" t="s">
         <v>296</v>
@@ -7373,18 +7373,18 @@
         <v>0.8</v>
       </c>
       <c r="G61" s="52" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H61" s="50" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="15" customHeight="1">
       <c r="A62" s="45" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B62" s="45" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C62" s="45" t="s">
         <v>27</v>
@@ -7401,15 +7401,15 @@
         <v>0.99</v>
       </c>
       <c r="G62" s="52" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H62" s="50" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="15" customHeight="1">
       <c r="A63" s="45" t="s">
-        <v>1104</v>
+        <v>1101</v>
       </c>
       <c r="B63" s="45" t="s">
         <v>51</v>
@@ -7429,15 +7429,15 @@
         <v>0.8</v>
       </c>
       <c r="G63" s="52" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H63" s="50" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="15" customHeight="1">
       <c r="A64" s="45" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B64" s="45" t="s">
         <v>355</v>
@@ -7457,15 +7457,15 @@
         <v>0.99</v>
       </c>
       <c r="G64" s="52" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H64" s="50" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="15" customHeight="1">
       <c r="A65" s="45" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B65" s="45" t="s">
         <v>351</v>
@@ -7485,15 +7485,15 @@
         <v>0.99</v>
       </c>
       <c r="G65" s="52" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H65" s="50" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="15" customHeight="1">
       <c r="A66" s="45" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B66" s="45" t="s">
         <v>359</v>
@@ -7513,15 +7513,15 @@
         <v>0.99</v>
       </c>
       <c r="G66" s="52" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H66" s="50" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="15" customHeight="1">
       <c r="A67" s="45" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B67" s="45" t="s">
         <v>257</v>
@@ -7541,18 +7541,18 @@
         <v>0.99</v>
       </c>
       <c r="G67" s="52" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H67" s="50" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="15" customHeight="1">
       <c r="A68" s="45" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B68" s="45" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C68" s="45" t="s">
         <v>333</v>
@@ -7569,18 +7569,18 @@
         <v>0.66</v>
       </c>
       <c r="G68" s="49" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H68" s="50" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="45" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B69" s="45" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C69" s="45" t="s">
         <v>324</v>
@@ -7597,18 +7597,18 @@
         <v>1</v>
       </c>
       <c r="G69" s="49" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H69" s="50" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="45" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B70" s="45" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C70" s="45" t="s">
         <v>352</v>
@@ -7625,15 +7625,15 @@
         <v>0</v>
       </c>
       <c r="G70" s="49" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H70" s="50" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="71" spans="1:8">
       <c r="A71" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B71" t="s">
         <v>246</v>
@@ -7653,15 +7653,15 @@
         <v>2</v>
       </c>
       <c r="G71" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H71" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="72" spans="1:8">
       <c r="A72" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B72" t="s">
         <v>246</v>
@@ -7681,10 +7681,10 @@
         <v>0.8</v>
       </c>
       <c r="G72" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H72" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
   </sheetData>
@@ -7713,30 +7713,30 @@
   <sheetData>
     <row r="1" spans="1:12" ht="18" customHeight="1">
       <c r="A1" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="G1" s="93" t="s">
         <v>559</v>
-      </c>
-      <c r="G1" s="93" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="G2" s="94" t="s">
         <v>561</v>
-      </c>
-      <c r="G2" s="94" t="s">
-        <v>562</v>
       </c>
       <c r="H2" s="95">
         <v>10</v>
       </c>
       <c r="I2" s="94" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="J2" s="95">
         <v>244</v>
       </c>
       <c r="K2" s="94" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="L2" s="96">
         <f>B25</f>
@@ -7749,21 +7749,21 @@
         <v/>
       </c>
       <c r="G3" s="94" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H3" s="98">
         <f>$J$2-$L$2</f>
         <v>3</v>
       </c>
       <c r="I3" s="94" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="J3" s="98">
         <f>ROUND($L$2*7/$H$2,1)</f>
         <v>168.7</v>
       </c>
       <c r="K3" s="94" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="L3" s="98" t="str">
         <f>IF($H$3&lt;0,"INVALID","VALID")</f>
@@ -7775,19 +7775,19 @@
         <v>5</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>567</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>568</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="D4" s="5" t="s">
         <v>569</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="E4" s="5" t="s">
         <v>570</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="F4" s="5" t="s">
         <v>571</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>572</v>
       </c>
       <c r="J4" s="99" t="str">
         <f>"주당 환산 (×7/"&amp;$H$2&amp;")"</f>
@@ -7815,10 +7815,10 @@
         <v>유지</v>
       </c>
       <c r="F5" s="53" t="s">
+        <v>572</v>
+      </c>
+      <c r="G5" s="115" t="s">
         <v>573</v>
-      </c>
-      <c r="G5" s="115" t="s">
-        <v>574</v>
       </c>
       <c r="H5" s="56">
         <f ca="1">SUM(D5:D6)</f>
@@ -7858,7 +7858,7 @@
         <v>성장</v>
       </c>
       <c r="F6" s="53" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="G6" s="116"/>
       <c r="J6" s="55">
@@ -7891,10 +7891,10 @@
         <v>성장</v>
       </c>
       <c r="F7" s="53" t="s">
+        <v>575</v>
+      </c>
+      <c r="G7" s="115" t="s">
         <v>576</v>
-      </c>
-      <c r="G7" s="115" t="s">
-        <v>577</v>
       </c>
       <c r="H7" s="56">
         <f ca="1">SUM(D7:D10)</f>
@@ -7930,7 +7930,7 @@
         <v>유지 미만</v>
       </c>
       <c r="F8" s="53" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="G8" s="116"/>
       <c r="J8" s="55">
@@ -7963,7 +7963,7 @@
         <v>유지</v>
       </c>
       <c r="F9" s="53" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="G9" s="116"/>
       <c r="J9" s="55">
@@ -7996,7 +7996,7 @@
         <v>성장</v>
       </c>
       <c r="F10" s="53" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="G10" s="116"/>
       <c r="J10" s="55">
@@ -8029,7 +8029,7 @@
         <v>유지</v>
       </c>
       <c r="F11" s="53" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="G11" s="57"/>
       <c r="J11" s="55">
@@ -8062,7 +8062,7 @@
         <v>성장</v>
       </c>
       <c r="F12" s="53" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G12" s="57"/>
       <c r="J12" s="55">
@@ -8095,7 +8095,7 @@
         <v>성장</v>
       </c>
       <c r="F13" s="53" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="G13" s="57"/>
       <c r="J13" s="55">
@@ -8128,7 +8128,7 @@
         <v>성장</v>
       </c>
       <c r="F14" s="53" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="G14" s="57"/>
       <c r="H14" s="56"/>
@@ -8165,7 +8165,7 @@
         <v>327</v>
       </c>
       <c r="G15" s="58" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H15" s="56">
         <f ca="1">SUM(D15:D16,D19)</f>
@@ -8201,7 +8201,7 @@
         <v>유지</v>
       </c>
       <c r="F16" s="53" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="G16" s="57"/>
       <c r="J16" s="55">
@@ -8234,7 +8234,7 @@
         <v>성장</v>
       </c>
       <c r="F17" s="53" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="G17" s="115" t="s">
         <v>324</v>
@@ -8273,7 +8273,7 @@
         <v>유지</v>
       </c>
       <c r="F18" s="53" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="G18" s="116"/>
       <c r="J18" s="55">
@@ -8306,7 +8306,7 @@
         <v>유지</v>
       </c>
       <c r="F19" s="53" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="G19" s="57"/>
       <c r="J19" s="55">
@@ -8339,7 +8339,7 @@
         <v>성장</v>
       </c>
       <c r="F20" s="53" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="G20" s="57"/>
       <c r="J20" s="55">
@@ -8372,7 +8372,7 @@
         <v>성장</v>
       </c>
       <c r="F21" s="53" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="G21" s="57"/>
       <c r="J21" s="55">
@@ -8405,7 +8405,7 @@
         <v>성장</v>
       </c>
       <c r="F22" s="53" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="G22" s="57"/>
       <c r="J22" s="55">
@@ -8438,7 +8438,7 @@
         <v>유지</v>
       </c>
       <c r="F23" s="53" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="G23" s="57"/>
       <c r="J23" s="55">
@@ -8471,7 +8471,7 @@
         <v>유지</v>
       </c>
       <c r="F24" s="53" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="G24" s="57"/>
       <c r="J24" s="55">
@@ -8485,7 +8485,7 @@
     </row>
     <row r="25" spans="1:12" ht="36" customHeight="1">
       <c r="A25" s="60" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B25" s="15">
         <f>SUM(B5:B24)</f>
@@ -8509,22 +8509,22 @@
     </row>
     <row r="26" spans="1:12" ht="15" customHeight="1">
       <c r="A26" s="13" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="16.5" customHeight="1">
       <c r="A27" s="11" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="36" customHeight="1">
       <c r="A28" s="11" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="48" customHeight="1">
       <c r="A29" s="11" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="48" customHeight="1">
@@ -8532,22 +8532,22 @@
     </row>
     <row r="31" spans="1:12" ht="15" customHeight="1">
       <c r="A31" s="13" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="16.5" customHeight="1">
       <c r="A32" s="11" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="48" customHeight="1">
       <c r="A33" s="11" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="48" customHeight="1">
       <c r="A34" s="11" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="15" customHeight="1">
@@ -8555,124 +8555,124 @@
     </row>
     <row r="36" spans="1:1" ht="48" customHeight="1">
       <c r="A36" s="13" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="77.25" customHeight="1">
       <c r="A37" s="11" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="38" spans="1:1" ht="48" customHeight="1">
       <c r="A38" s="11" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="39" spans="1:1" ht="39" customHeight="1">
       <c r="A39" s="63" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="40" spans="1:1" ht="45" customHeight="1">
       <c r="A40" s="11" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="41" spans="1:1" ht="48" customHeight="1">
       <c r="A41" s="11" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="42" spans="1:1" ht="48" customHeight="1">
       <c r="A42" s="11" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="43" spans="1:1" ht="48" customHeight="1">
       <c r="A43" s="11" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="44" spans="1:1" ht="48" customHeight="1">
       <c r="A44" s="90" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="45" spans="1:1" ht="51.75" customHeight="1">
       <c r="A45" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="46" spans="1:1" ht="90" customHeight="1">
       <c r="A46" s="11" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="47" spans="1:1" ht="51.75" customHeight="1">
       <c r="A47" s="11" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="48" spans="1:1" ht="48" customHeight="1">
       <c r="A48" s="11" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="48" customHeight="1">
       <c r="A49" s="11" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="48" customHeight="1">
       <c r="A50" s="11" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="93" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="100" t="s">
+        <v>624</v>
+      </c>
+      <c r="B58" s="100" t="s">
         <v>625</v>
       </c>
-      <c r="B58" s="100" t="s">
+      <c r="C58" s="100" t="s">
         <v>626</v>
       </c>
-      <c r="C58" s="100" t="s">
+      <c r="D58" s="100" t="s">
         <v>627</v>
       </c>
-      <c r="D58" s="100" t="s">
+      <c r="E58" s="100" t="s">
         <v>628</v>
-      </c>
-      <c r="E58" s="100" t="s">
-        <v>629</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -8686,7 +8686,7 @@
         <v>239</v>
       </c>
       <c r="D59" s="102" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="E59" s="102" t="s">
         <v>150</v>
@@ -8703,10 +8703,10 @@
         <v>239</v>
       </c>
       <c r="D60" s="107" t="s">
+        <v>630</v>
+      </c>
+      <c r="E60" s="107" t="s">
         <v>631</v>
-      </c>
-      <c r="E60" s="107" t="s">
-        <v>632</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -8720,45 +8720,45 @@
         <v>244</v>
       </c>
       <c r="D61" s="111" t="s">
+        <v>632</v>
+      </c>
+      <c r="E61" s="111" t="s">
         <v>633</v>
-      </c>
-      <c r="E61" s="111" t="s">
-        <v>634</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="104" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
   </sheetData>
@@ -8808,50 +8808,50 @@
   <sheetData>
     <row r="1" spans="1:13" ht="18" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="15" customHeight="1">
       <c r="A5" s="64" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C5" s="4">
         <v>5</v>
       </c>
       <c r="D5" s="63" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="15" customHeight="1">
       <c r="A6" s="64" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C6" s="4">
         <v>5</v>
       </c>
       <c r="D6" s="63" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1">
       <c r="A7" s="64" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C7" s="4">
         <v>2.25</v>
       </c>
       <c r="D7" s="63" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H7">
         <f>SUM(D7:D10)</f>
@@ -8860,13 +8860,13 @@
     </row>
     <row r="8" spans="1:13" ht="84" customHeight="1">
       <c r="A8" s="64" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C8" s="4">
         <v>1.25</v>
       </c>
       <c r="D8" s="63" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="15" customHeight="1">
@@ -8874,40 +8874,40 @@
         <v>128</v>
       </c>
       <c r="B9" s="5" t="s">
+        <v>652</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>653</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="D9" s="5" t="s">
         <v>654</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="E9" s="5" t="s">
         <v>655</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="F9" s="5" t="s">
+        <v>654</v>
+      </c>
+      <c r="G9" s="5" t="s">
         <v>656</v>
       </c>
-      <c r="F9" s="5" t="s">
-        <v>655</v>
-      </c>
-      <c r="G9" s="5" t="s">
+      <c r="H9" s="5" t="s">
+        <v>654</v>
+      </c>
+      <c r="I9" s="5" t="s">
         <v>657</v>
       </c>
-      <c r="H9" s="5" t="s">
-        <v>655</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>658</v>
-      </c>
       <c r="J9" s="5" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="K9" s="5" t="s">
         <v>13</v>
       </c>
       <c r="L9" s="100" t="s">
+        <v>658</v>
+      </c>
+      <c r="M9" s="100" t="s">
         <v>659</v>
-      </c>
-      <c r="M9" s="100" t="s">
-        <v>660</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15" customHeight="1">
@@ -9264,17 +9264,17 @@
     </row>
     <row r="23" spans="1:13" ht="108" customHeight="1">
       <c r="A23" s="11" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="84" customHeight="1">
       <c r="A24" s="11" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="84" customHeight="1">
       <c r="A25" s="11" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="120" customHeight="1">
@@ -9282,52 +9282,52 @@
     </row>
     <row r="27" spans="1:13" ht="96" customHeight="1">
       <c r="A27" s="11" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="108" customHeight="1">
       <c r="A28" s="11" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="108" customHeight="1">
       <c r="A29" s="11" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="156" customHeight="1">
       <c r="A30" s="11" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="96" customHeight="1">
       <c r="A31" s="11" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="32" spans="1:13">
       <c r="A32" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
   </sheetData>
@@ -9348,45 +9348,45 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18" customHeight="1">
       <c r="A1" s="66" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1">
       <c r="A4" s="5" t="s">
+        <v>675</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>676</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="C4" s="5" t="s">
         <v>677</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>678</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1">
       <c r="A5" s="7" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B5" s="7" t="s">
+        <v>678</v>
+      </c>
+      <c r="C5" s="53" t="s">
         <v>679</v>
-      </c>
-      <c r="C5" s="53" t="s">
-        <v>680</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1">
       <c r="A6" s="7" t="s">
+        <v>680</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>678</v>
+      </c>
+      <c r="C6" s="53" t="s">
         <v>681</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>679</v>
-      </c>
-      <c r="C6" s="53" t="s">
-        <v>682</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1">
@@ -9394,80 +9394,80 @@
         <v>273</v>
       </c>
       <c r="B7" s="7" t="s">
+        <v>682</v>
+      </c>
+      <c r="C7" s="53" t="s">
         <v>683</v>
-      </c>
-      <c r="C7" s="53" t="s">
-        <v>684</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1">
       <c r="A8" s="67" t="s">
+        <v>684</v>
+      </c>
+      <c r="B8" s="67" t="s">
         <v>685</v>
       </c>
-      <c r="B8" s="67" t="s">
+      <c r="C8" s="68" t="s">
         <v>686</v>
-      </c>
-      <c r="C8" s="68" t="s">
-        <v>687</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15" customHeight="1">
       <c r="A9" s="67" t="s">
+        <v>687</v>
+      </c>
+      <c r="B9" s="67" t="s">
+        <v>685</v>
+      </c>
+      <c r="C9" s="68" t="s">
         <v>688</v>
-      </c>
-      <c r="B9" s="67" t="s">
-        <v>686</v>
-      </c>
-      <c r="C9" s="68" t="s">
-        <v>689</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15" customHeight="1">
       <c r="A10" s="7" t="s">
+        <v>689</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>690</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="C10" s="69" t="s">
         <v>691</v>
-      </c>
-      <c r="C10" s="69" t="s">
-        <v>692</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1">
       <c r="A11" s="7" t="s">
+        <v>692</v>
+      </c>
+      <c r="B11" s="8" t="s">
         <v>693</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="C11" s="53" t="s">
         <v>694</v>
-      </c>
-      <c r="C11" s="53" t="s">
-        <v>695</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15" customHeight="1">
       <c r="A12" s="7" t="s">
+        <v>695</v>
+      </c>
+      <c r="B12" s="7" t="s">
         <v>696</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="C12" s="53" t="s">
         <v>697</v>
-      </c>
-      <c r="C12" s="53" t="s">
-        <v>698</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="24" customHeight="1">
       <c r="A15" s="11" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="24" customHeight="1">
       <c r="A16" s="11" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="36" customHeight="1">
       <c r="A17" s="11" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="15" customHeight="1">
@@ -9475,47 +9475,47 @@
     </row>
     <row r="19" spans="1:1" ht="36" customHeight="1">
       <c r="A19" s="11" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="36" customHeight="1">
       <c r="A20" s="11" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="48" customHeight="1">
       <c r="A22" s="13" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="16.5" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="16.5" customHeight="1">
       <c r="A25" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="16.5" customHeight="1">
       <c r="A26" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="27" spans="1:1" ht="16.5" customHeight="1">
       <c r="A27" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="16.5" customHeight="1">
       <c r="A28" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="16.5" customHeight="1">
       <c r="A30" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
   </sheetData>
@@ -9541,31 +9541,31 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1">
       <c r="A2" s="70" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="16.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15" customHeight="1">
       <c r="A5" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>714</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="C5" s="5" t="s">
         <v>715</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="D5" s="5" t="s">
         <v>716</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>717</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>7</v>
@@ -9574,111 +9574,111 @@
         <v>148</v>
       </c>
       <c r="G5" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15" customHeight="1">
       <c r="A6" s="71" t="s">
+        <v>718</v>
+      </c>
+      <c r="B6" s="72" t="s">
         <v>719</v>
       </c>
-      <c r="B6" s="72" t="s">
+      <c r="C6" s="72" t="s">
         <v>720</v>
       </c>
-      <c r="C6" s="72" t="s">
+      <c r="D6" s="71" t="s">
         <v>721</v>
-      </c>
-      <c r="D6" s="71" t="s">
-        <v>722</v>
       </c>
       <c r="E6" s="71">
         <f>복귀_평일A_가슴!$E$12</f>
         <v>28</v>
       </c>
       <c r="F6" s="73" t="s">
+        <v>722</v>
+      </c>
+      <c r="G6" t="s">
         <v>723</v>
-      </c>
-      <c r="G6" t="s">
-        <v>724</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15" customHeight="1">
       <c r="A7" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>719</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>720</v>
+      </c>
+      <c r="D7" s="67" t="s">
         <v>725</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>720</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>721</v>
-      </c>
-      <c r="D7" s="67" t="s">
-        <v>726</v>
       </c>
       <c r="E7" s="7">
         <f>복귀_평일B_어깨!$E$15</f>
         <v>35</v>
       </c>
       <c r="F7" s="69" t="s">
+        <v>726</v>
+      </c>
+      <c r="G7" t="s">
         <v>727</v>
-      </c>
-      <c r="G7" t="s">
-        <v>728</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15" customHeight="1">
       <c r="A8" s="71" t="s">
+        <v>728</v>
+      </c>
+      <c r="B8" s="72" t="s">
         <v>729</v>
       </c>
-      <c r="B8" s="72" t="s">
+      <c r="C8" s="72" t="s">
+        <v>715</v>
+      </c>
+      <c r="D8" s="71" t="s">
         <v>730</v>
-      </c>
-      <c r="C8" s="72" t="s">
-        <v>716</v>
-      </c>
-      <c r="D8" s="71" t="s">
-        <v>731</v>
       </c>
       <c r="E8" s="71">
         <f>복귀_토_하체!$E$14</f>
         <v>32</v>
       </c>
       <c r="F8" s="73" t="s">
+        <v>731</v>
+      </c>
+      <c r="G8" t="s">
         <v>732</v>
-      </c>
-      <c r="G8" t="s">
-        <v>733</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15" customHeight="1">
       <c r="A9" s="71" t="s">
+        <v>733</v>
+      </c>
+      <c r="B9" s="72" t="s">
         <v>734</v>
       </c>
-      <c r="B9" s="72" t="s">
+      <c r="C9" s="72" t="s">
+        <v>715</v>
+      </c>
+      <c r="D9" s="71" t="s">
         <v>735</v>
-      </c>
-      <c r="C9" s="72" t="s">
-        <v>716</v>
-      </c>
-      <c r="D9" s="71" t="s">
-        <v>736</v>
       </c>
       <c r="E9" s="71">
         <f>복귀_일_등!$E$16</f>
         <v>33</v>
       </c>
       <c r="F9" s="73" t="s">
+        <v>736</v>
+      </c>
+      <c r="G9" t="s">
         <v>737</v>
-      </c>
-      <c r="G9" t="s">
-        <v>738</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15" customHeight="1">
       <c r="A10" s="71" t="s">
+        <v>738</v>
+      </c>
+      <c r="B10" s="72" t="s">
         <v>739</v>
-      </c>
-      <c r="B10" s="72" t="s">
-        <v>740</v>
       </c>
       <c r="C10" s="72" t="s">
         <v>150</v>
@@ -9693,7 +9693,7 @@
         <v>150</v>
       </c>
       <c r="G10" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15" customHeight="1">
@@ -9708,7 +9708,7 @@
         <v>128</v>
       </c>
       <c r="F11" s="53" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1">
@@ -9729,32 +9729,32 @@
     </row>
     <row r="15" spans="1:7" ht="48" customHeight="1">
       <c r="A15" s="13" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="141" customHeight="1">
       <c r="A16" s="11" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="126" customHeight="1">
       <c r="A17" s="11" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="77.25" customHeight="1">
       <c r="A18" s="11" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="115.5" customHeight="1">
       <c r="A19" s="11" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="15" customHeight="1">
       <c r="A20" s="63" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="48" customHeight="1">
@@ -9762,22 +9762,22 @@
     </row>
     <row r="22" spans="1:1" ht="141" customHeight="1">
       <c r="A22" s="11" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="77.25" customHeight="1">
       <c r="A23" s="11" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="90" customHeight="1">
       <c r="A24" s="11" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="128.25" customHeight="1">
       <c r="A25" s="11" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="128.25" customHeight="1">
@@ -9785,32 +9785,32 @@
     </row>
     <row r="27" spans="1:1" ht="15" customHeight="1">
       <c r="A27" s="63" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="48" customHeight="1">
       <c r="A28" s="13" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="29" spans="1:1" ht="75" customHeight="1">
       <c r="A29" s="11" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="102.75" customHeight="1">
       <c r="A30" s="11" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="90" customHeight="1">
       <c r="A31" s="11" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="32" spans="1:1" ht="128.25" customHeight="1">
       <c r="A32" s="11" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="144" customHeight="1">
@@ -9818,47 +9818,47 @@
     </row>
     <row r="34" spans="1:1" ht="15" customHeight="1">
       <c r="A34" s="74" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="45" spans="1:1">
@@ -9868,27 +9868,27 @@
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
   </sheetData>
@@ -9919,12 +9919,12 @@
   <sheetData>
     <row r="1" spans="1:13" ht="21" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1">
@@ -9999,10 +9999,10 @@
         <v>17.5</v>
       </c>
       <c r="J5" t="s">
+        <v>774</v>
+      </c>
+      <c r="K5" t="s">
         <v>775</v>
-      </c>
-      <c r="K5" t="s">
-        <v>776</v>
       </c>
       <c r="L5" s="68" t="s">
         <v>295</v>
@@ -10013,7 +10013,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="68" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="C6" s="67" t="s">
         <v>27</v>
@@ -10039,13 +10039,13 @@
         <v>10.5</v>
       </c>
       <c r="J6" t="s">
+        <v>777</v>
+      </c>
+      <c r="K6" t="s">
         <v>778</v>
       </c>
-      <c r="K6" t="s">
-        <v>779</v>
-      </c>
       <c r="L6" s="68" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1">
@@ -10078,10 +10078,10 @@
         <v>13</v>
       </c>
       <c r="J7" t="s">
+        <v>779</v>
+      </c>
+      <c r="K7" t="s">
         <v>780</v>
-      </c>
-      <c r="K7" t="s">
-        <v>781</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="15" customHeight="1">
@@ -10089,7 +10089,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="53" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>318</v>
@@ -10114,10 +10114,10 @@
         <v>8</v>
       </c>
       <c r="J8" t="s">
+        <v>781</v>
+      </c>
+      <c r="K8" t="s">
         <v>782</v>
-      </c>
-      <c r="K8" t="s">
-        <v>783</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="15" customHeight="1">
@@ -10125,7 +10125,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="53" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>333</v>
@@ -10150,10 +10150,10 @@
         <v>9</v>
       </c>
       <c r="J9" t="s">
+        <v>783</v>
+      </c>
+      <c r="K9" t="s">
         <v>784</v>
-      </c>
-      <c r="K9" t="s">
-        <v>785</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15" customHeight="1">
@@ -10167,7 +10167,7 @@
         <v>337</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="E10" s="7">
         <v>4</v>
@@ -10186,10 +10186,10 @@
         <v>10.7</v>
       </c>
       <c r="J10" t="s">
+        <v>786</v>
+      </c>
+      <c r="K10" t="s">
         <v>787</v>
-      </c>
-      <c r="K10" t="s">
-        <v>788</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="15" customHeight="1">
@@ -10222,10 +10222,10 @@
         <v>5.8</v>
       </c>
       <c r="J11" t="s">
+        <v>788</v>
+      </c>
+      <c r="K11" t="s">
         <v>789</v>
-      </c>
-      <c r="K11" t="s">
-        <v>790</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="15" customHeight="1">
@@ -10233,13 +10233,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="87" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="C12" t="s">
         <v>23</v>
       </c>
       <c r="D12" s="76" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="E12" s="28">
         <v>3</v>
@@ -10258,10 +10258,10 @@
         <v>5</v>
       </c>
       <c r="J12" t="s">
+        <v>792</v>
+      </c>
+      <c r="K12" t="s">
         <v>793</v>
-      </c>
-      <c r="K12" t="s">
-        <v>794</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -10294,10 +10294,10 @@
         <v>6.7</v>
       </c>
       <c r="J13" t="s">
+        <v>794</v>
+      </c>
+      <c r="K13" t="s">
         <v>795</v>
-      </c>
-      <c r="K13" t="s">
-        <v>796</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="76.5" customHeight="1">
@@ -10320,72 +10320,72 @@
     </row>
     <row r="16" spans="1:13" ht="293.25" customHeight="1">
       <c r="A16" s="11" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="276" customHeight="1">
       <c r="A17" s="11" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="33" spans="3:3">
       <c r="C33" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
   </sheetData>
@@ -10416,12 +10416,12 @@
   <sheetData>
     <row r="1" spans="1:13" ht="21" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1">
@@ -10496,10 +10496,10 @@
         <v>3.5</v>
       </c>
       <c r="J5" t="s">
+        <v>811</v>
+      </c>
+      <c r="K5" t="s">
         <v>812</v>
-      </c>
-      <c r="K5" t="s">
-        <v>813</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="15" customHeight="1">
@@ -10507,13 +10507,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="89" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>247</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="E6" s="7">
         <v>4</v>
@@ -10532,13 +10532,13 @@
         <v>12.7</v>
       </c>
       <c r="J6" t="s">
+        <v>815</v>
+      </c>
+      <c r="K6" t="s">
         <v>816</v>
       </c>
-      <c r="K6" t="s">
+      <c r="L6" s="53" t="s">
         <v>817</v>
-      </c>
-      <c r="L6" s="53" t="s">
-        <v>818</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1">
@@ -10546,7 +10546,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="89" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>238</v>
@@ -10571,10 +10571,10 @@
         <v>12.7</v>
       </c>
       <c r="J7" t="s">
+        <v>819</v>
+      </c>
+      <c r="K7" t="s">
         <v>820</v>
-      </c>
-      <c r="K7" t="s">
-        <v>821</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="15" customHeight="1">
@@ -10607,13 +10607,13 @@
         <v>9.3000000000000007</v>
       </c>
       <c r="J8" t="s">
+        <v>821</v>
+      </c>
+      <c r="K8" t="s">
         <v>822</v>
       </c>
-      <c r="K8" t="s">
+      <c r="L8" s="53" t="s">
         <v>823</v>
-      </c>
-      <c r="L8" s="53" t="s">
-        <v>824</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="29.25" customHeight="1">
@@ -10627,7 +10627,7 @@
         <v>247</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="E9" s="7">
         <v>3</v>
@@ -10646,10 +10646,10 @@
         <v>5.8</v>
       </c>
       <c r="J9" t="s">
+        <v>825</v>
+      </c>
+      <c r="K9" t="s">
         <v>826</v>
-      </c>
-      <c r="K9" t="s">
-        <v>827</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15" customHeight="1">
@@ -10663,7 +10663,7 @@
         <v>34</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="E10" s="7">
         <v>3</v>
@@ -10682,10 +10682,10 @@
         <v>5.8</v>
       </c>
       <c r="J10" t="s">
+        <v>827</v>
+      </c>
+      <c r="K10" t="s">
         <v>828</v>
-      </c>
-      <c r="K10" t="s">
-        <v>829</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="15" customHeight="1">
@@ -10718,13 +10718,13 @@
         <v>8</v>
       </c>
       <c r="J11" t="s">
+        <v>829</v>
+      </c>
+      <c r="K11" t="s">
         <v>830</v>
       </c>
-      <c r="K11" t="s">
+      <c r="L11" s="53" t="s">
         <v>831</v>
-      </c>
-      <c r="L11" s="53" t="s">
-        <v>832</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="15" customHeight="1">
@@ -10757,10 +10757,10 @@
         <v>7.3</v>
       </c>
       <c r="J12" t="s">
+        <v>832</v>
+      </c>
+      <c r="K12" t="s">
         <v>833</v>
-      </c>
-      <c r="K12" t="s">
-        <v>834</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="15" customHeight="1">
@@ -10793,10 +10793,10 @@
         <v>5.8</v>
       </c>
       <c r="J13" t="s">
+        <v>834</v>
+      </c>
+      <c r="K13" t="s">
         <v>835</v>
-      </c>
-      <c r="K13" t="s">
-        <v>836</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -10804,7 +10804,7 @@
         <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="C14" t="s">
         <v>45</v>
@@ -10829,10 +10829,10 @@
         <v>5</v>
       </c>
       <c r="J14" t="s">
+        <v>837</v>
+      </c>
+      <c r="K14" t="s">
         <v>838</v>
-      </c>
-      <c r="K14" t="s">
-        <v>839</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="17.25" customHeight="1">
@@ -10865,10 +10865,10 @@
         <v>5</v>
       </c>
       <c r="J15" t="s">
+        <v>839</v>
+      </c>
+      <c r="K15" t="s">
         <v>840</v>
-      </c>
-      <c r="K15" t="s">
-        <v>841</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="23.25" customHeight="1">
@@ -10891,112 +10891,112 @@
     </row>
     <row r="18" spans="1:1" ht="278.25" customHeight="1">
       <c r="A18" s="11" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="15" customHeight="1">
       <c r="A19" s="63" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="95.25" customHeight="1">
       <c r="A20" s="12" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="252.75" customHeight="1">
       <c r="A21" s="11" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="237.75" customHeight="1">
       <c r="A22" s="11" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="265.5" customHeight="1">
       <c r="A23" s="11" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="C44" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
     </row>
   </sheetData>
@@ -11027,12 +11027,12 @@
   <sheetData>
     <row r="1" spans="1:13" ht="21" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1">
@@ -11106,7 +11106,7 @@
         <v>10.7</v>
       </c>
       <c r="J5" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="K5" t="s">
         <v>32</v>
@@ -11142,10 +11142,10 @@
         <v>6.7</v>
       </c>
       <c r="J6" t="s">
+        <v>866</v>
+      </c>
+      <c r="K6" t="s">
         <v>867</v>
-      </c>
-      <c r="K6" t="s">
-        <v>868</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1">
@@ -11153,13 +11153,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="53" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>18</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="E7" s="7">
         <v>4</v>
@@ -11178,10 +11178,10 @@
         <v>8</v>
       </c>
       <c r="J7" t="s">
+        <v>870</v>
+      </c>
+      <c r="K7" t="s">
         <v>871</v>
-      </c>
-      <c r="K7" t="s">
-        <v>872</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="15" customHeight="1">
@@ -11189,7 +11189,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="53" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>23</v>
@@ -11214,10 +11214,10 @@
         <v>6.7</v>
       </c>
       <c r="J8" t="s">
+        <v>872</v>
+      </c>
+      <c r="K8" t="s">
         <v>873</v>
-      </c>
-      <c r="K8" t="s">
-        <v>874</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="15" customHeight="1">
@@ -11231,7 +11231,7 @@
         <v>23</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="E9" s="7">
         <v>3</v>
@@ -11250,10 +11250,10 @@
         <v>5</v>
       </c>
       <c r="J9" t="s">
+        <v>874</v>
+      </c>
+      <c r="K9" t="s">
         <v>875</v>
-      </c>
-      <c r="K9" t="s">
-        <v>876</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15" customHeight="1">
@@ -11286,10 +11286,10 @@
         <v>5.8</v>
       </c>
       <c r="J10" t="s">
+        <v>876</v>
+      </c>
+      <c r="K10" t="s">
         <v>877</v>
-      </c>
-      <c r="K10" t="s">
-        <v>878</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="15" customHeight="1">
@@ -11297,13 +11297,13 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C11" t="s">
         <v>324</v>
       </c>
       <c r="D11" s="76" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="E11" s="28">
         <v>3</v>
@@ -11322,10 +11322,10 @@
         <v>8</v>
       </c>
       <c r="J11" t="s">
+        <v>879</v>
+      </c>
+      <c r="K11" t="s">
         <v>880</v>
-      </c>
-      <c r="K11" t="s">
-        <v>881</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -11358,10 +11358,10 @@
         <v>6.8</v>
       </c>
       <c r="J12" t="s">
+        <v>881</v>
+      </c>
+      <c r="K12" t="s">
         <v>882</v>
-      </c>
-      <c r="K12" t="s">
-        <v>883</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="18.75" customHeight="1">
@@ -11394,10 +11394,10 @@
         <v>10.7</v>
       </c>
       <c r="J13" t="s">
+        <v>883</v>
+      </c>
+      <c r="K13" t="s">
         <v>884</v>
-      </c>
-      <c r="K13" t="s">
-        <v>885</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="18" customHeight="1">
@@ -11405,7 +11405,7 @@
         <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C14" s="87" t="s">
         <v>262</v>
@@ -11430,10 +11430,10 @@
         <v>5</v>
       </c>
       <c r="J14" t="s">
+        <v>885</v>
+      </c>
+      <c r="K14" t="s">
         <v>886</v>
-      </c>
-      <c r="K14" t="s">
-        <v>887</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="25.5" customHeight="1">
@@ -11452,72 +11452,72 @@
     </row>
     <row r="16" spans="1:13" ht="237.75" customHeight="1">
       <c r="A16" s="11" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
     </row>
     <row r="33" spans="3:3">
       <c r="C33" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
   </sheetData>
@@ -11548,12 +11548,12 @@
   <sheetData>
     <row r="1" spans="1:13" ht="21" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1">
@@ -11628,10 +11628,10 @@
         <v>17.5</v>
       </c>
       <c r="J5" t="s">
+        <v>902</v>
+      </c>
+      <c r="K5" t="s">
         <v>903</v>
-      </c>
-      <c r="K5" t="s">
-        <v>904</v>
       </c>
       <c r="L5" s="68" t="s">
         <v>295</v>
@@ -11642,13 +11642,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="53" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>301</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="E6" s="7">
         <v>5</v>
@@ -11667,10 +11667,10 @@
         <v>15.8</v>
       </c>
       <c r="J6" t="s">
+        <v>904</v>
+      </c>
+      <c r="K6" t="s">
         <v>905</v>
-      </c>
-      <c r="K6" t="s">
-        <v>906</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1">
@@ -11678,7 +11678,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="53" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>301</v>
@@ -11703,10 +11703,10 @@
         <v>9.6999999999999993</v>
       </c>
       <c r="J7" t="s">
+        <v>907</v>
+      </c>
+      <c r="K7" t="s">
         <v>908</v>
-      </c>
-      <c r="K7" t="s">
-        <v>909</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="15" customHeight="1">
@@ -11739,10 +11739,10 @@
         <v>12.7</v>
       </c>
       <c r="J8" t="s">
+        <v>909</v>
+      </c>
+      <c r="K8" t="s">
         <v>910</v>
-      </c>
-      <c r="K8" t="s">
-        <v>911</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="15" customHeight="1">
@@ -11750,7 +11750,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="89" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>238</v>
@@ -11775,10 +11775,10 @@
         <v>10.7</v>
       </c>
       <c r="J9" t="s">
+        <v>912</v>
+      </c>
+      <c r="K9" t="s">
         <v>913</v>
-      </c>
-      <c r="K9" t="s">
-        <v>914</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15" customHeight="1">
@@ -11811,10 +11811,10 @@
         <v>5.8</v>
       </c>
       <c r="J10" t="s">
+        <v>914</v>
+      </c>
+      <c r="K10" t="s">
         <v>915</v>
-      </c>
-      <c r="K10" t="s">
-        <v>916</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="15" customHeight="1">
@@ -11847,10 +11847,10 @@
         <v>5.5</v>
       </c>
       <c r="J11" t="s">
+        <v>916</v>
+      </c>
+      <c r="K11" t="s">
         <v>917</v>
-      </c>
-      <c r="K11" t="s">
-        <v>918</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -11882,27 +11882,27 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="C27" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
     </row>
   </sheetData>
@@ -11914,7 +11914,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F94"/>
+  <dimension ref="A1:F95"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -11986,7 +11986,7 @@
         <v>153</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="E6" s="20">
         <f>INDEX(D2_밀기A!$E:$E,MATCH("세트 합계",D2_밀기A!$D:$D,0))</f>
@@ -12030,15 +12030,15 @@
         <v>150</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>1101</v>
+        <v>1119</v>
       </c>
       <c r="E8" s="20">
         <f>INDEX(D4_어깨팔A!$E:$E,MATCH("세트 합계",D4_어깨팔A!$D:$D,0))</f>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F8" s="20" t="str">
         <f>"약 "&amp;INDEX(D4_어깨팔A!$I:$I,MATCH("세트 합계",D4_어깨팔A!$D:$D,0))&amp;"분"</f>
-        <v>약 70분</v>
+        <v>약 71분</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15" customHeight="1">
@@ -12072,15 +12072,15 @@
         <v>150</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>1116</v>
+        <v>1120</v>
       </c>
       <c r="E10" s="20">
         <f>INDEX(D6_당기기B!$E:$E,MATCH("세트 합계",D6_당기기B!$D:$D,0))</f>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F10" s="20" t="str">
         <f>"약 "&amp;INDEX(D6_당기기B!$I:$I,MATCH("세트 합계",D6_당기기B!$D:$D,0))&amp;"분"</f>
-        <v>약 72분</v>
+        <v>약 71분</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15" customHeight="1">
@@ -12094,7 +12094,7 @@
         <v>161</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>1117</v>
+        <v>1111</v>
       </c>
       <c r="E11" s="20">
         <f>INDEX(D7_밀기B!$E:$E,MATCH("세트 합계",D7_밀기B!$D:$D,0))</f>
@@ -12138,7 +12138,7 @@
         <v>150</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>1102</v>
+        <v>1099</v>
       </c>
       <c r="E13" s="20">
         <f>INDEX(D9_어깨팔B!$E:$E,MATCH("세트 합계",D9_어깨팔B!$D:$D,0))</f>
@@ -12276,283 +12276,288 @@
     </row>
     <row r="35" spans="1:1" ht="90" customHeight="1">
       <c r="A35" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="36" spans="1:1" ht="90" customHeight="1">
       <c r="A36" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="90" customHeight="1">
       <c r="A37" t="s">
-        <v>1103</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="38" spans="1:1" ht="90" customHeight="1">
       <c r="A38" t="s">
-        <v>1118</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" ht="51.75" customHeight="1">
-      <c r="A39" s="13" t="s">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" ht="90" customHeight="1">
+      <c r="A39" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" ht="51.75" customHeight="1">
+      <c r="A40" s="13" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="40" spans="1:1" ht="77.25" customHeight="1">
-      <c r="A40" s="30" t="s">
+    <row r="41" spans="1:1" ht="77.25" customHeight="1">
+      <c r="A41" s="30" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="41" spans="1:1" ht="64.5" customHeight="1">
-      <c r="A41" s="30" t="s">
+    <row r="42" spans="1:1" ht="64.5" customHeight="1">
+      <c r="A42" s="30" t="s">
         <v>186</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" ht="16.5" customHeight="1">
-      <c r="A42" s="30" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="43" spans="1:1" ht="16.5" customHeight="1">
       <c r="A43" s="30" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="44" spans="1:1" ht="16.5" customHeight="1">
       <c r="A44" s="30" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" ht="16.5" customHeight="1">
+      <c r="A45" s="30" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="45" spans="1:1" ht="242.25" customHeight="1">
-      <c r="A45" s="30"/>
-    </row>
-    <row r="46" spans="1:1" ht="270.75" customHeight="1">
-      <c r="A46" s="13" t="s">
+    <row r="46" spans="1:1" ht="242.25" customHeight="1">
+      <c r="A46" s="30"/>
+    </row>
+    <row r="47" spans="1:1" ht="270.75" customHeight="1">
+      <c r="A47" s="13" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="47" spans="1:1" ht="242.25" customHeight="1">
-      <c r="A47" s="30" t="s">
+    <row r="48" spans="1:1" ht="242.25" customHeight="1">
+      <c r="A48" s="30" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="48" spans="1:1" ht="199.5" customHeight="1">
-      <c r="A48" s="30" t="s">
+    <row r="49" spans="1:1" ht="199.5" customHeight="1">
+      <c r="A49" s="30" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="49" spans="1:1" ht="185.25" customHeight="1">
-      <c r="A49" s="30" t="s">
+    <row r="50" spans="1:1" ht="185.25" customHeight="1">
+      <c r="A50" s="30" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="50" spans="1:1" ht="199.5" customHeight="1">
-      <c r="A50" s="30" t="s">
+    <row r="51" spans="1:1" ht="199.5" customHeight="1">
+      <c r="A51" s="30" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="51" spans="1:1" ht="185.25" customHeight="1">
-      <c r="A51" s="30" t="s">
+    <row r="52" spans="1:1" ht="185.25" customHeight="1">
+      <c r="A52" s="30" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="52" spans="1:1" ht="327.75" customHeight="1">
-      <c r="A52" s="30" t="s">
+    <row r="53" spans="1:1" ht="327.75" customHeight="1">
+      <c r="A53" s="30" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="53" spans="1:1" ht="256.5" customHeight="1">
-      <c r="A53" s="32"/>
-    </row>
-    <row r="54" spans="1:1" ht="409.5" customHeight="1">
-      <c r="A54" s="13" t="s">
+    <row r="54" spans="1:1" ht="256.5" customHeight="1">
+      <c r="A54" s="32"/>
+    </row>
+    <row r="55" spans="1:1" ht="409.5" customHeight="1">
+      <c r="A55" s="13" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="55" spans="1:1" ht="370.5" customHeight="1">
-      <c r="A55" s="30" t="s">
+    <row r="56" spans="1:1" ht="370.5" customHeight="1">
+      <c r="A56" s="30" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="56" spans="1:1" ht="409.5" customHeight="1">
-      <c r="A56" s="30" t="s">
+    <row r="57" spans="1:1" ht="409.5" customHeight="1">
+      <c r="A57" s="30" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="57" spans="1:1" ht="370.5" customHeight="1">
-      <c r="A57" s="30" t="s">
+    <row r="58" spans="1:1" ht="370.5" customHeight="1">
+      <c r="A58" s="30" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="58" spans="1:1" ht="185.25" customHeight="1">
-      <c r="A58" s="30" t="s">
+    <row r="59" spans="1:1" ht="185.25" customHeight="1">
+      <c r="A59" s="30" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="59" spans="1:1" ht="60" customHeight="1">
-      <c r="A59" s="31"/>
-    </row>
-    <row r="60" spans="1:1" ht="256.5" customHeight="1">
-      <c r="A60" s="13" t="s">
+    <row r="60" spans="1:1" ht="60" customHeight="1">
+      <c r="A60" s="31"/>
+    </row>
+    <row r="61" spans="1:1" ht="256.5" customHeight="1">
+      <c r="A61" s="13" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="61" spans="1:1" ht="327.75" customHeight="1">
-      <c r="A61" s="30" t="s">
+    <row r="62" spans="1:1" ht="327.75" customHeight="1">
+      <c r="A62" s="30" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="62" spans="1:1" ht="256.5" customHeight="1">
-      <c r="A62" s="30" t="s">
+    <row r="63" spans="1:1" ht="256.5" customHeight="1">
+      <c r="A63" s="30" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="63" spans="1:1" ht="409.5" customHeight="1">
-      <c r="A63" s="30" t="s">
+    <row r="64" spans="1:1" ht="409.5" customHeight="1">
+      <c r="A64" s="30" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="64" spans="1:1" ht="370.5" customHeight="1">
-      <c r="A64" s="30" t="s">
+    <row r="65" spans="1:1" ht="370.5" customHeight="1">
+      <c r="A65" s="30" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="65" spans="1:1" ht="285" customHeight="1">
-      <c r="A65" s="30" t="s">
+    <row r="66" spans="1:1" ht="285" customHeight="1">
+      <c r="A66" s="30" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="66" spans="1:1" ht="90" customHeight="1">
-      <c r="A66" s="30" t="s">
+    <row r="67" spans="1:1" ht="90" customHeight="1">
+      <c r="A67" s="30" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="67" spans="1:1" ht="313.5" customHeight="1">
-      <c r="A67" s="13" t="s">
+    <row r="68" spans="1:1" ht="313.5" customHeight="1">
+      <c r="A68" s="13" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="68" spans="1:1" ht="370.5" customHeight="1">
-      <c r="A68" s="30" t="s">
+    <row r="69" spans="1:1" ht="370.5" customHeight="1">
+      <c r="A69" s="30" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="69" spans="1:1" ht="285" customHeight="1">
-      <c r="A69" s="30" t="s">
+    <row r="70" spans="1:1" ht="285" customHeight="1">
+      <c r="A70" s="30" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="70" spans="1:1" ht="370.5" customHeight="1"/>
-    <row r="71" spans="1:1" ht="256.5" customHeight="1">
-      <c r="A71" s="13" t="s">
+    <row r="71" spans="1:1" ht="370.5" customHeight="1"/>
+    <row r="72" spans="1:1" ht="256.5" customHeight="1">
+      <c r="A72" s="13" t="s">
         <v>212</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" ht="327.75" customHeight="1">
-      <c r="A72" s="30" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="73" spans="1:1" ht="327.75" customHeight="1">
       <c r="A73" s="30" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" ht="327.75" customHeight="1">
+      <c r="A74" s="30" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="74" spans="1:1" ht="299.25" customHeight="1">
-      <c r="A74" s="30" t="s">
+    <row r="75" spans="1:1" ht="299.25" customHeight="1">
+      <c r="A75" s="30" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="75" spans="1:1" ht="327.75" customHeight="1">
-      <c r="A75" s="30" t="s">
+    <row r="76" spans="1:1" ht="327.75" customHeight="1">
+      <c r="A76" s="30" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="76" spans="1:1" ht="90" customHeight="1"/>
-    <row r="77" spans="1:1" ht="75" customHeight="1">
-      <c r="A77" s="13" t="s">
+    <row r="77" spans="1:1" ht="90" customHeight="1"/>
+    <row r="78" spans="1:1" ht="75" customHeight="1">
+      <c r="A78" s="13" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="78" spans="1:1" ht="327.75" customHeight="1">
-      <c r="A78" s="30" t="s">
+    <row r="79" spans="1:1" ht="327.75" customHeight="1">
+      <c r="A79" s="30" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="79" spans="1:1" ht="356.25" customHeight="1">
-      <c r="A79" s="30" t="s">
+    <row r="80" spans="1:1" ht="356.25" customHeight="1">
+      <c r="A80" s="30" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="80" spans="1:1" ht="270.75" customHeight="1">
-      <c r="A80" s="30" t="s">
+    <row r="81" spans="1:1" ht="270.75" customHeight="1">
+      <c r="A81" s="30" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="81" spans="1:1" ht="313.5" customHeight="1">
-      <c r="A81" s="30" t="s">
+    <row r="82" spans="1:1" ht="313.5" customHeight="1">
+      <c r="A82" s="30" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="82" spans="1:1" ht="142.5" customHeight="1">
-      <c r="A82" s="30" t="s">
+    <row r="83" spans="1:1" ht="142.5" customHeight="1">
+      <c r="A83" s="30" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="83" spans="1:1" ht="242.25" customHeight="1">
-      <c r="A83" s="30" t="s">
+    <row r="84" spans="1:1" ht="242.25" customHeight="1">
+      <c r="A84" s="30" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="84" spans="1:1" ht="299.25" customHeight="1">
-      <c r="A84" s="30" t="s">
+    <row r="85" spans="1:1" ht="299.25" customHeight="1">
+      <c r="A85" s="30" t="s">
         <v>224</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1" ht="327.75" customHeight="1">
-      <c r="A85" s="30" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="86" spans="1:1" ht="327.75" customHeight="1">
       <c r="A86" s="30" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" ht="327.75" customHeight="1">
+      <c r="A87" s="30" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="87" spans="1:1" ht="75" customHeight="1"/>
-    <row r="88" spans="1:1" ht="327.75" customHeight="1">
-      <c r="A88" s="13" t="s">
+    <row r="88" spans="1:1" ht="75" customHeight="1"/>
+    <row r="89" spans="1:1" ht="327.75" customHeight="1">
+      <c r="A89" s="13" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="89" spans="1:1" ht="356.25" customHeight="1">
-      <c r="A89" s="30" t="s">
+    <row r="90" spans="1:1" ht="356.25" customHeight="1">
+      <c r="A90" s="30" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="90" spans="1:1" ht="270.75" customHeight="1">
-      <c r="A90" s="30" t="s">
+    <row r="91" spans="1:1" ht="270.75" customHeight="1">
+      <c r="A91" s="30" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="91" spans="1:1" ht="313.5" customHeight="1">
-      <c r="A91" s="30" t="s">
+    <row r="92" spans="1:1" ht="313.5" customHeight="1">
+      <c r="A92" s="30" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="92" spans="1:1" ht="142.5" customHeight="1">
-      <c r="A92" s="30" t="s">
+    <row r="93" spans="1:1" ht="142.5" customHeight="1">
+      <c r="A93" s="30" t="s">
         <v>231</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1" ht="242.25" customHeight="1">
-      <c r="A93" s="30" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="94" spans="1:1" ht="242.25" customHeight="1">
       <c r="A94" s="30" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" ht="242.25" customHeight="1">
+      <c r="A95" s="30" t="s">
         <v>233</v>
       </c>
     </row>
@@ -12575,166 +12580,166 @@
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
       <c r="A4" s="5" t="s">
+        <v>925</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>926</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="C4" s="5" t="s">
         <v>927</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>928</v>
-      </c>
       <c r="D4" s="5" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1">
       <c r="A5" s="7" t="s">
+        <v>928</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>929</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="C5" s="7" t="s">
         <v>930</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="D5" s="69" t="s">
         <v>931</v>
-      </c>
-      <c r="D5" s="69" t="s">
-        <v>932</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1">
       <c r="A6" s="7" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B6" s="8" t="s">
+        <v>932</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="D6" s="53" t="s">
         <v>934</v>
-      </c>
-      <c r="D6" s="53" t="s">
-        <v>935</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1">
       <c r="A7" s="7" t="s">
+        <v>935</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>936</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="C7" s="7" t="s">
         <v>937</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="D7" s="53" t="s">
         <v>938</v>
-      </c>
-      <c r="D7" s="53" t="s">
-        <v>939</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1">
       <c r="A8" s="7" t="s">
+        <v>939</v>
+      </c>
+      <c r="B8" s="7" t="s">
         <v>940</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="C8" s="7" t="s">
         <v>941</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="D8" s="53" t="s">
         <v>942</v>
-      </c>
-      <c r="D8" s="53" t="s">
-        <v>943</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15" customHeight="1">
       <c r="A9" s="7" t="s">
+        <v>943</v>
+      </c>
+      <c r="B9" s="8" t="s">
         <v>944</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="C9" s="8" t="s">
         <v>945</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="D9" s="53" t="s">
         <v>946</v>
-      </c>
-      <c r="D9" s="53" t="s">
-        <v>947</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15" customHeight="1">
       <c r="A10" s="7" t="s">
+        <v>947</v>
+      </c>
+      <c r="B10" s="8" t="s">
         <v>948</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="C10" s="8" t="s">
         <v>949</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="D10" s="53" t="s">
         <v>950</v>
-      </c>
-      <c r="D10" s="53" t="s">
-        <v>951</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15" customHeight="1">
       <c r="A11" s="7" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>150</v>
       </c>
       <c r="C11" s="8" t="s">
+        <v>952</v>
+      </c>
+      <c r="D11" s="53" t="s">
         <v>953</v>
-      </c>
-      <c r="D11" s="53" t="s">
-        <v>954</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15" customHeight="1">
       <c r="A12" s="7" t="s">
+        <v>954</v>
+      </c>
+      <c r="B12" s="8" t="s">
         <v>955</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="C12" s="8" t="s">
         <v>956</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="D12" s="53" t="s">
         <v>957</v>
-      </c>
-      <c r="D12" s="53" t="s">
-        <v>958</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15" customHeight="1">
       <c r="A13" s="79" t="s">
+        <v>958</v>
+      </c>
+      <c r="B13" s="80" t="s">
         <v>959</v>
       </c>
-      <c r="B13" s="80" t="s">
+      <c r="C13" s="80" t="s">
         <v>960</v>
       </c>
-      <c r="C13" s="80" t="s">
+      <c r="D13" s="79" t="s">
         <v>961</v>
-      </c>
-      <c r="D13" s="79" t="s">
-        <v>962</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
+        <v>962</v>
+      </c>
+      <c r="B14" t="s">
         <v>963</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>964</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>965</v>
-      </c>
-      <c r="D14" t="s">
-        <v>966</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1">
@@ -12745,22 +12750,22 @@
     </row>
     <row r="17" spans="1:1" ht="51.75" customHeight="1">
       <c r="A17" s="11" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="39" customHeight="1">
       <c r="A18" s="11" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="39" customHeight="1">
       <c r="A19" s="11" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="15" customHeight="1">
       <c r="A20" s="63" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="51.75" customHeight="1">
@@ -12768,137 +12773,137 @@
     </row>
     <row r="22" spans="1:1" ht="39" customHeight="1">
       <c r="A22" s="11" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="15" customHeight="1">
       <c r="A23" s="63" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="51.75" customHeight="1">
       <c r="A24" s="11" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="39" customHeight="1">
       <c r="A25" s="11" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
     </row>
   </sheetData>
@@ -12924,17 +12929,17 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F3">
         <f ca="1">COUNTIF($E$7:$E$51,"?")</f>
@@ -12943,38 +12948,38 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="B6" t="s">
+        <v>476</v>
+      </c>
+      <c r="C6" t="s">
         <v>477</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>478</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>479</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>480</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>481</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>482</v>
-      </c>
-      <c r="H6" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="B7" t="s">
         <v>387</v>
@@ -12994,18 +12999,18 @@
         <v>0.8</v>
       </c>
       <c r="G7" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H7" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="B8" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="C8" t="s">
         <v>44</v>
@@ -13022,18 +13027,18 @@
         <v>2</v>
       </c>
       <c r="G8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H8" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B9" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="C9" t="s">
         <v>44</v>
@@ -13050,18 +13055,18 @@
         <v>0.8</v>
       </c>
       <c r="G9" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H9" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B10" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="C10" t="s">
         <v>44</v>
@@ -13078,15 +13083,15 @@
         <v>1.32</v>
       </c>
       <c r="G10" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H10" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B11" t="s">
         <v>237</v>
@@ -13106,15 +13111,15 @@
         <v>1.5</v>
       </c>
       <c r="G11" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H11" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="B12" t="s">
         <v>103</v>
@@ -13134,18 +13139,18 @@
         <v>2.5</v>
       </c>
       <c r="G12" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H12" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="B13" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C13" t="s">
         <v>39</v>
@@ -13162,15 +13167,15 @@
         <v>2.5</v>
       </c>
       <c r="G13" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H13" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B15" t="s">
         <v>26</v>
@@ -13190,18 +13195,18 @@
         <v>2</v>
       </c>
       <c r="G15" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H15" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B16" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="C16" t="s">
         <v>39</v>
@@ -13218,15 +13223,15 @@
         <v>1.5</v>
       </c>
       <c r="G16" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H16" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B17" t="s">
         <v>296</v>
@@ -13246,15 +13251,15 @@
         <v>1.5</v>
       </c>
       <c r="G17" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H17" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="B18" t="s">
         <v>103</v>
@@ -13274,18 +13279,18 @@
         <v>2.5</v>
       </c>
       <c r="G18" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H18" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="B19" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C19" t="s">
         <v>27</v>
@@ -13302,15 +13307,15 @@
         <v>2.5</v>
       </c>
       <c r="G19" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H19" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B20" t="s">
         <v>296</v>
@@ -13330,18 +13335,18 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="G20" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H20" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B21" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="C21" t="s">
         <v>18</v>
@@ -13358,15 +13363,15 @@
         <v>1.5</v>
       </c>
       <c r="G21" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H21" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="B22" t="s">
         <v>387</v>
@@ -13386,18 +13391,18 @@
         <v>2</v>
       </c>
       <c r="G22" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H22" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B23" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="C23" t="s">
         <v>238</v>
@@ -13414,18 +13419,18 @@
         <v>2</v>
       </c>
       <c r="G23" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H23" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B24" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="C24" t="s">
         <v>247</v>
@@ -13442,15 +13447,15 @@
         <v>2</v>
       </c>
       <c r="G24" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H24" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B25" t="s">
         <v>355</v>
@@ -13470,18 +13475,18 @@
         <v>1.5</v>
       </c>
       <c r="G25" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H25" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B26" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C26" t="s">
         <v>247</v>
@@ -13498,18 +13503,18 @@
         <v>1.32</v>
       </c>
       <c r="G26" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H26" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B27" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="C27" t="s">
         <v>247</v>
@@ -13526,18 +13531,18 @@
         <v>0.99</v>
       </c>
       <c r="G27" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H27" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B28" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="C28" t="s">
         <v>352</v>
@@ -13554,18 +13559,18 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="G28" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H28" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B29" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="C29" t="s">
         <v>352</v>
@@ -13582,15 +13587,15 @@
         <v>0.8</v>
       </c>
       <c r="G29" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H29" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B30" t="s">
         <v>101</v>
@@ -13610,15 +13615,15 @@
         <v>0.2</v>
       </c>
       <c r="G30" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H30" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B31" t="s">
         <v>237</v>
@@ -13638,18 +13643,18 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="G31" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H31" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="B32" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="C32" t="s">
         <v>34</v>
@@ -13666,15 +13671,15 @@
         <v>0.8</v>
       </c>
       <c r="G32" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H32" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B33" t="s">
         <v>99</v>
@@ -13694,18 +13699,18 @@
         <v>1</v>
       </c>
       <c r="G33" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H33" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B34" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="C34" t="s">
         <v>273</v>
@@ -13722,15 +13727,15 @@
         <v>0.8</v>
       </c>
       <c r="G34" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H34" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B35" t="s">
         <v>407</v>
@@ -13750,15 +13755,15 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="G35" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H35" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B36" t="s">
         <v>99</v>
@@ -13778,15 +13783,15 @@
         <v>2.5</v>
       </c>
       <c r="G36" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H36" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B37" t="s">
         <v>101</v>
@@ -13806,15 +13811,15 @@
         <v>0.5</v>
       </c>
       <c r="G37" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H37" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B38" t="s">
         <v>323</v>
@@ -13834,18 +13839,18 @@
         <v>1.32</v>
       </c>
       <c r="G38" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H38" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B39" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C39" t="s">
         <v>333</v>
@@ -13862,15 +13867,15 @@
         <v>1.5</v>
       </c>
       <c r="G39" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H39" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B40" t="s">
         <v>101</v>
@@ -13890,15 +13895,15 @@
         <v>0.5</v>
       </c>
       <c r="G40" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H40" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B41" t="s">
         <v>99</v>
@@ -13918,15 +13923,15 @@
         <v>1</v>
       </c>
       <c r="G41" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H41" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B42" t="s">
         <v>323</v>
@@ -13946,15 +13951,15 @@
         <v>0.8</v>
       </c>
       <c r="G42" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H42" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B43" t="s">
         <v>43</v>
@@ -13974,15 +13979,15 @@
         <v>0.99</v>
       </c>
       <c r="G43" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H43" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B44" t="s">
         <v>400</v>
@@ -14002,15 +14007,15 @@
         <v>0.99</v>
       </c>
       <c r="G44" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H44" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="B45" t="s">
         <v>103</v>
@@ -14030,18 +14035,18 @@
         <v>1</v>
       </c>
       <c r="G45" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H45" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="B46" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C46" t="s">
         <v>290</v>
@@ -14058,15 +14063,15 @@
         <v>1</v>
       </c>
       <c r="G46" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H46" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B47" t="s">
         <v>101</v>
@@ -14086,15 +14091,15 @@
         <v>0</v>
       </c>
       <c r="G47" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H47" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B48" t="s">
         <v>99</v>
@@ -14114,15 +14119,15 @@
         <v>0</v>
       </c>
       <c r="G48" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H48" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B49" t="s">
         <v>55</v>
@@ -14142,18 +14147,18 @@
         <v>0</v>
       </c>
       <c r="G49" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H49" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="B50" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="C50" t="s">
         <v>290</v>
@@ -14170,18 +14175,18 @@
         <v>0.8</v>
       </c>
       <c r="G50" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H50" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="B51" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="C51" t="s">
         <v>27</v>
@@ -14198,10 +14203,10 @@
         <v>0.8</v>
       </c>
       <c r="G51" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H51" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
   </sheetData>
@@ -14227,12 +14232,12 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -14240,22 +14245,22 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
+        <v>567</v>
+      </c>
+      <c r="C4" t="s">
         <v>568</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>569</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>570</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>571</v>
       </c>
-      <c r="F4" t="s">
-        <v>572</v>
-      </c>
       <c r="G4" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -14279,13 +14284,13 @@
         <v>충분</v>
       </c>
       <c r="F5" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="G5" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H5" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="I5">
         <f ca="1">SUM(D5:D6)</f>
@@ -14313,10 +14318,10 @@
         <v>충분</v>
       </c>
       <c r="F6" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="G6" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -14340,13 +14345,13 @@
         <v>충분</v>
       </c>
       <c r="F7" t="s">
+        <v>1042</v>
+      </c>
+      <c r="G7" t="s">
         <v>1043</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>1044</v>
-      </c>
-      <c r="H7" t="s">
-        <v>1045</v>
       </c>
       <c r="I7">
         <f ca="1">SUM(D7:D10)</f>
@@ -14374,10 +14379,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F8" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="G8" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -14401,10 +14406,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F9" t="s">
+        <v>1046</v>
+      </c>
+      <c r="G9" t="s">
         <v>1047</v>
-      </c>
-      <c r="G9" t="s">
-        <v>1048</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -14428,10 +14433,10 @@
         <v>충분</v>
       </c>
       <c r="F10" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="G10" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -14455,10 +14460,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F11" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="G11" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -14482,10 +14487,10 @@
         <v>충분</v>
       </c>
       <c r="F12" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="G12" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -14509,10 +14514,10 @@
         <v>충분</v>
       </c>
       <c r="F13" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="G13" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -14536,10 +14541,10 @@
         <v>충분</v>
       </c>
       <c r="F14" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="G14" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -14563,13 +14568,13 @@
         <v>충분</v>
       </c>
       <c r="F15" t="s">
+        <v>1053</v>
+      </c>
+      <c r="G15" t="s">
+        <v>1043</v>
+      </c>
+      <c r="H15" t="s">
         <v>1054</v>
-      </c>
-      <c r="G15" t="s">
-        <v>1044</v>
-      </c>
-      <c r="H15" t="s">
-        <v>1055</v>
       </c>
       <c r="I15">
         <f ca="1">SUM(D15:D16,D19)</f>
@@ -14597,10 +14602,10 @@
         <v>하한</v>
       </c>
       <c r="F16" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="G16" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -14624,10 +14629,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F17" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="G17" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -14651,10 +14656,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F18" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="G18" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -14678,10 +14683,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F19" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="G19" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -14705,10 +14710,10 @@
         <v>충분</v>
       </c>
       <c r="F20" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="G20" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -14732,10 +14737,10 @@
         <v>충분</v>
       </c>
       <c r="F21" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="G21" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -14759,10 +14764,10 @@
         <v>하한</v>
       </c>
       <c r="F22" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="G22" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -14786,10 +14791,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F23" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="G23" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -14813,15 +14818,15 @@
         <v>보완 필요</v>
       </c>
       <c r="F24" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="G24" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B25">
         <f>SUM(B5:B24)</f>
@@ -14834,67 +14839,67 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
   </sheetData>
@@ -15403,7 +15408,7 @@
   </sheetData>
   <phoneticPr fontId="32" type="noConversion"/>
   <conditionalFormatting sqref="A6:N15">
-    <cfRule type="expression" dxfId="13" priority="1">
+    <cfRule type="expression" dxfId="12" priority="1">
       <formula>$E6=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15439,7 +15444,7 @@
     </row>
     <row r="2" spans="1:3" ht="16.5" customHeight="1">
       <c r="A2" s="18" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="16.5" customHeight="1">
@@ -15817,7 +15822,7 @@
       </c>
       <c r="J25" s="21"/>
       <c r="K25" s="21" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="L25" s="21" t="s">
         <v>368</v>
@@ -15840,7 +15845,7 @@
   </sheetData>
   <phoneticPr fontId="32" type="noConversion"/>
   <conditionalFormatting sqref="A20:N25">
-    <cfRule type="expression" dxfId="12" priority="1">
+    <cfRule type="expression" dxfId="11" priority="1">
       <formula>$E20=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16298,7 +16303,7 @@
   </sheetData>
   <phoneticPr fontId="32" type="noConversion"/>
   <conditionalFormatting sqref="A15:N21">
-    <cfRule type="expression" dxfId="11" priority="1">
+    <cfRule type="expression" dxfId="10" priority="1">
       <formula>$E15=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16331,7 +16336,7 @@
     </row>
     <row r="2" spans="1:14" ht="16.5" customHeight="1">
       <c r="A2" s="18" t="s">
-        <v>1108</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="30" customHeight="1">
@@ -16546,155 +16551,155 @@
       <c r="A10" s="20">
         <v>5</v>
       </c>
-      <c r="B10" s="21" t="s">
-        <v>300</v>
+      <c r="B10" s="91" t="s">
+        <v>407</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>301</v>
-      </c>
-      <c r="D10" s="42" t="s">
-        <v>302</v>
+        <v>34</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>408</v>
       </c>
       <c r="E10" s="20">
         <v>3</v>
       </c>
       <c r="F10" s="26" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="G10" s="26">
         <v>40</v>
       </c>
       <c r="H10" s="26">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="I10" s="26">
         <f t="shared" si="0"/>
-        <v>9.5</v>
-      </c>
-      <c r="J10" s="21" t="s">
-        <v>303</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="J10" s="21"/>
       <c r="K10" s="21" t="s">
-        <v>1078</v>
-      </c>
-      <c r="L10" s="36" t="s">
-        <v>304</v>
-      </c>
-      <c r="M10" s="92"/>
+        <v>1113</v>
+      </c>
+      <c r="L10" s="21" t="s">
+        <v>409</v>
+      </c>
     </row>
     <row r="11" spans="1:14" ht="16.5" customHeight="1">
       <c r="A11" s="20">
         <v>6</v>
       </c>
       <c r="B11" s="21" t="s">
-        <v>363</v>
+        <v>300</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>290</v>
-      </c>
-      <c r="D11" s="26" t="s">
-        <v>364</v>
+        <v>301</v>
+      </c>
+      <c r="D11" s="42" t="s">
+        <v>302</v>
       </c>
       <c r="E11" s="20">
         <v>3</v>
       </c>
       <c r="F11" s="26" t="s">
-        <v>306</v>
+        <v>40</v>
       </c>
       <c r="G11" s="26">
         <v>40</v>
       </c>
       <c r="H11" s="26">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="I11" s="26">
         <f t="shared" si="0"/>
-        <v>6.5</v>
+        <v>9.5</v>
       </c>
       <c r="J11" s="21" t="s">
-        <v>27</v>
+        <v>303</v>
       </c>
       <c r="K11" s="21" t="s">
-        <v>365</v>
-      </c>
-      <c r="L11" s="21" t="s">
-        <v>366</v>
-      </c>
+        <v>1077</v>
+      </c>
+      <c r="L11" s="36" t="s">
+        <v>304</v>
+      </c>
+      <c r="M11" s="92"/>
     </row>
     <row r="12" spans="1:14" ht="16.5" customHeight="1">
       <c r="A12" s="20">
         <v>7</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>257</v>
-      </c>
-      <c r="C12" s="43" t="s">
-        <v>44</v>
+        <v>363</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>290</v>
       </c>
       <c r="D12" s="26" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="E12" s="20">
         <v>3</v>
       </c>
       <c r="F12" s="26" t="s">
-        <v>40</v>
+        <v>306</v>
       </c>
       <c r="G12" s="26">
         <v>40</v>
       </c>
       <c r="H12" s="26">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="I12" s="26">
         <f t="shared" si="0"/>
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="J12" s="21" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="K12" s="21" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="L12" s="21" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="16.5" customHeight="1">
       <c r="A13" s="20">
         <v>8</v>
       </c>
-      <c r="B13" s="81" t="s">
-        <v>48</v>
-      </c>
-      <c r="C13" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="D13" s="20">
-        <v>15</v>
+      <c r="B13" s="21" t="s">
+        <v>257</v>
+      </c>
+      <c r="C13" s="43" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="26" t="s">
+        <v>369</v>
       </c>
       <c r="E13" s="20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F13" s="26" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="G13" s="26">
         <v>40</v>
       </c>
       <c r="H13" s="26">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="I13" s="26">
         <f t="shared" si="0"/>
-        <v>6.7</v>
-      </c>
-      <c r="J13" s="21"/>
+        <v>5.5</v>
+      </c>
+      <c r="J13" s="21" t="s">
+        <v>45</v>
+      </c>
       <c r="K13" s="21" t="s">
-        <v>1091</v>
+        <v>370</v>
       </c>
       <c r="L13" s="21" t="s">
-        <v>50</v>
+        <v>371</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="16.5" customHeight="1">
@@ -16702,7 +16707,7 @@
         <v>9</v>
       </c>
       <c r="B14" s="81" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C14" s="20" t="s">
         <v>45</v>
@@ -16714,80 +16719,80 @@
         <v>4</v>
       </c>
       <c r="F14" s="26" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G14" s="26">
         <v>40</v>
       </c>
       <c r="H14" s="26">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I14" s="26">
         <f t="shared" si="0"/>
-        <v>7.3</v>
-      </c>
-      <c r="J14" s="21" t="s">
-        <v>53</v>
-      </c>
+        <v>6.7</v>
+      </c>
+      <c r="J14" s="21"/>
       <c r="K14" s="21" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="L14" s="21" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="16.5" customHeight="1">
       <c r="A15" s="20">
         <v>10</v>
       </c>
-      <c r="B15" s="21" t="s">
-        <v>268</v>
+      <c r="B15" s="81" t="s">
+        <v>51</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="D15" s="26">
-        <v>10</v>
+        <v>45</v>
+      </c>
+      <c r="D15" s="20">
+        <v>15</v>
       </c>
       <c r="E15" s="20">
         <v>4</v>
       </c>
       <c r="F15" s="26" t="s">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="G15" s="26">
         <v>40</v>
       </c>
       <c r="H15" s="26">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="I15" s="26">
         <f t="shared" si="0"/>
-        <v>7.7</v>
-      </c>
-      <c r="J15" s="21"/>
+        <v>7.3</v>
+      </c>
+      <c r="J15" s="21" t="s">
+        <v>53</v>
+      </c>
       <c r="K15" s="21" t="s">
-        <v>1106</v>
+        <v>1091</v>
       </c>
       <c r="L15" s="21" t="s">
-        <v>411</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="16.5" customHeight="1">
       <c r="A16" s="20">
         <v>11</v>
       </c>
-      <c r="B16" s="81" t="s">
-        <v>55</v>
+      <c r="B16" s="21" t="s">
+        <v>268</v>
       </c>
       <c r="C16" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="D16" s="20" t="s">
-        <v>57</v>
+      <c r="D16" s="26">
+        <v>10</v>
       </c>
       <c r="E16" s="20">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F16" s="26" t="s">
         <v>19</v>
@@ -16800,14 +16805,14 @@
       </c>
       <c r="I16" s="26">
         <f t="shared" si="0"/>
-        <v>3.8</v>
+        <v>7.7</v>
       </c>
       <c r="J16" s="21"/>
       <c r="K16" s="21" t="s">
-        <v>1093</v>
+        <v>1103</v>
       </c>
       <c r="L16" s="21" t="s">
-        <v>58</v>
+        <v>410</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="16.5" customHeight="1">
@@ -16816,11 +16821,11 @@
       </c>
       <c r="E17" s="27">
         <f>SUM(E6:E16)</f>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I17">
         <f>ROUND(SUM(I6:I16),0)</f>
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="16.5" customHeight="1"/>
@@ -16851,7 +16856,7 @@
     </row>
     <row r="24" spans="1:9" ht="16.5" customHeight="1">
       <c r="A24" s="109" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="16.5" customHeight="1">
@@ -16866,7 +16871,7 @@
     </row>
     <row r="27" spans="1:9" ht="16.5" customHeight="1">
       <c r="A27" s="108" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="16.5" customHeight="1">
@@ -16877,37 +16882,41 @@
     <row r="29" spans="1:9" ht="16.5" customHeight="1"/>
     <row r="30" spans="1:9" ht="16.5" customHeight="1">
       <c r="A30" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="16.5" customHeight="1">
       <c r="A31" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="16.5" customHeight="1">
       <c r="A32" t="s">
-        <v>1112</v>
-      </c>
-    </row>
-    <row r="33" ht="16.5" customHeight="1"/>
-    <row r="34" ht="16.5" customHeight="1"/>
-    <row r="35" ht="16.5" customHeight="1"/>
-    <row r="36" ht="16.5" customHeight="1"/>
-    <row r="37" ht="16.5" customHeight="1"/>
-    <row r="38" ht="16.5" customHeight="1"/>
-    <row r="39" ht="16.5" customHeight="1"/>
-    <row r="40" ht="16.5" customHeight="1"/>
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" ht="16.5" customHeight="1">
+      <c r="A33" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" ht="16.5" customHeight="1"/>
+    <row r="35" spans="1:1" ht="16.5" customHeight="1"/>
+    <row r="36" spans="1:1" ht="16.5" customHeight="1"/>
+    <row r="37" spans="1:1" ht="16.5" customHeight="1"/>
+    <row r="38" spans="1:1" ht="16.5" customHeight="1"/>
+    <row r="39" spans="1:1" ht="16.5" customHeight="1"/>
+    <row r="40" spans="1:1" ht="16.5" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="32" type="noConversion"/>
-  <conditionalFormatting sqref="A6:N14 A16:N16">
-    <cfRule type="expression" dxfId="10" priority="2">
+  <conditionalFormatting sqref="A6:N9 A11:N16">
+    <cfRule type="expression" dxfId="9" priority="2">
       <formula>$E6=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A15:N15">
-    <cfRule type="expression" dxfId="9" priority="1">
-      <formula>$E15=0</formula>
+  <conditionalFormatting sqref="A10:N10">
+    <cfRule type="expression" dxfId="8" priority="1">
+      <formula>$E10=0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -16938,7 +16947,7 @@
     </row>
     <row r="2" spans="1:14" ht="16.5" customHeight="1">
       <c r="A2" s="18" t="s">
-        <v>1110</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -17233,17 +17242,17 @@
       <c r="A12" s="20">
         <v>7</v>
       </c>
-      <c r="B12" s="91" t="s">
-        <v>407</v>
+      <c r="B12" s="81" t="s">
+        <v>55</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>408</v>
+        <v>57</v>
       </c>
       <c r="E12" s="20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F12" s="26" t="s">
         <v>19</v>
@@ -17252,18 +17261,18 @@
         <v>40</v>
       </c>
       <c r="H12" s="26">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="I12" s="26">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="J12" s="21"/>
       <c r="K12" s="21" t="s">
-        <v>409</v>
+        <v>1114</v>
       </c>
       <c r="L12" s="21" t="s">
-        <v>410</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="16.5" customHeight="1">
@@ -17297,7 +17306,7 @@
       </c>
       <c r="J13" s="21"/>
       <c r="K13" s="21" t="s">
-        <v>1105</v>
+        <v>1102</v>
       </c>
       <c r="L13" s="21" t="s">
         <v>62</v>
@@ -17346,21 +17355,26 @@
       </c>
       <c r="E15" s="27">
         <f>SUM(E6:E14)</f>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I15">
         <f>ROUND(SUM(I6:I14),0)</f>
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="15" customHeight="1">
       <c r="A16" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>1113</v>
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>1118</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -17368,14 +17382,14 @@
     </row>
   </sheetData>
   <phoneticPr fontId="32" type="noConversion"/>
-  <conditionalFormatting sqref="A6:N12 A14:N14">
-    <cfRule type="expression" dxfId="8" priority="2">
+  <conditionalFormatting sqref="A6:N11 A13:N14">
+    <cfRule type="expression" dxfId="7" priority="2">
       <formula>$E6=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A13:N13">
-    <cfRule type="expression" dxfId="7" priority="1">
-      <formula>$E13=0</formula>
+  <conditionalFormatting sqref="A12:N12">
+    <cfRule type="expression" dxfId="6" priority="1">
+      <formula>$E12=0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -17402,17 +17416,17 @@
   <sheetData>
     <row r="1" spans="1:3" ht="19.5" customHeight="1">
       <c r="A1" s="17" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="16.5" customHeight="1">
       <c r="A2" s="18" t="s">
-        <v>1111</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="16.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="16.5" customHeight="1">
@@ -17565,7 +17579,7 @@
         <v>1</v>
       </c>
       <c r="B20" s="39" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C20" s="40" t="s">
         <v>27</v>
@@ -17594,13 +17608,13 @@
         <v>30</v>
       </c>
       <c r="K20" s="39" t="s">
+        <v>416</v>
+      </c>
+      <c r="L20" s="39" t="s">
         <v>417</v>
       </c>
-      <c r="L20" s="39" t="s">
+      <c r="M20" s="38" t="s">
         <v>418</v>
-      </c>
-      <c r="M20" s="38" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="16.5" customHeight="1">
@@ -17633,13 +17647,13 @@
         <v>8</v>
       </c>
       <c r="J21" s="21" t="s">
+        <v>419</v>
+      </c>
+      <c r="K21" s="21" t="s">
         <v>420</v>
       </c>
-      <c r="K21" s="21" t="s">
+      <c r="L21" s="21" t="s">
         <v>421</v>
-      </c>
-      <c r="L21" s="21" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="16.5" customHeight="1">
@@ -17675,10 +17689,10 @@
         <v>250</v>
       </c>
       <c r="K22" s="21" t="s">
+        <v>422</v>
+      </c>
+      <c r="L22" s="21" t="s">
         <v>423</v>
-      </c>
-      <c r="L22" s="21" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="16.5" customHeight="1">
@@ -17686,7 +17700,7 @@
         <v>4</v>
       </c>
       <c r="B23" s="21" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C23" s="20" t="s">
         <v>290</v>
@@ -17714,10 +17728,10 @@
         <v>39</v>
       </c>
       <c r="K23" s="21" t="s">
+        <v>425</v>
+      </c>
+      <c r="L23" s="21" t="s">
         <v>426</v>
-      </c>
-      <c r="L23" s="21" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="16.5" customHeight="1">
@@ -17725,7 +17739,7 @@
         <v>5</v>
       </c>
       <c r="B24" s="21" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C24" s="20" t="s">
         <v>301</v>
@@ -17753,10 +17767,10 @@
         <v>292</v>
       </c>
       <c r="K24" s="21" t="s">
+        <v>428</v>
+      </c>
+      <c r="L24" s="21" t="s">
         <v>429</v>
-      </c>
-      <c r="L24" s="21" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="16.5" customHeight="1">
@@ -17790,10 +17804,10 @@
       </c>
       <c r="J25" s="21"/>
       <c r="K25" s="21" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="L25" s="21" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="16.5" customHeight="1">
@@ -17801,7 +17815,7 @@
         <v>7</v>
       </c>
       <c r="B26" s="21" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C26" s="20" t="s">
         <v>23</v>
@@ -17827,10 +17841,10 @@
       </c>
       <c r="J26" s="21"/>
       <c r="K26" s="21" t="s">
+        <v>431</v>
+      </c>
+      <c r="L26" s="21" t="s">
         <v>432</v>
-      </c>
-      <c r="L26" s="21" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="16.5" customHeight="1">
@@ -17838,7 +17852,7 @@
         <v>8</v>
       </c>
       <c r="B27" s="21" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C27" s="20" t="s">
         <v>18</v>
@@ -17864,10 +17878,10 @@
       </c>
       <c r="J27" s="21"/>
       <c r="K27" s="21" t="s">
+        <v>434</v>
+      </c>
+      <c r="L27" s="21" t="s">
         <v>435</v>
-      </c>
-      <c r="L27" s="21" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="16.5" customHeight="1">
@@ -17903,10 +17917,10 @@
         <v>395</v>
       </c>
       <c r="K28" s="21" t="s">
+        <v>436</v>
+      </c>
+      <c r="L28" s="21" t="s">
         <v>437</v>
-      </c>
-      <c r="L28" s="21" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="16.5" customHeight="1">
@@ -17914,7 +17928,7 @@
         <v>10</v>
       </c>
       <c r="B29" s="85" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C29" s="20" t="s">
         <v>262</v>
@@ -17940,10 +17954,10 @@
       </c>
       <c r="J29" s="21"/>
       <c r="K29" s="21" t="s">
-        <v>1107</v>
+        <v>1104</v>
       </c>
       <c r="L29" s="21" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="15" customHeight="1">
@@ -17970,70 +17984,65 @@
     </row>
     <row r="31" spans="1:14" ht="15" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="31" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="16.5" customHeight="1">
       <c r="A33" s="31" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="16.5" customHeight="1">
       <c r="A34" s="31" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="16.5" customHeight="1">
       <c r="A35" s="31" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="36" spans="1:1" ht="16.5" customHeight="1">
       <c r="A36" s="31" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="16.5" customHeight="1">
       <c r="A37" s="31" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="38" spans="1:1" ht="16.5" customHeight="1">
       <c r="A38" s="31" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="39" spans="1:1" ht="16.5" customHeight="1"/>
     <row r="40" spans="1:1" ht="16.5" customHeight="1">
       <c r="A40" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>1114</v>
+        <v>1109</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="32" type="noConversion"/>
-  <conditionalFormatting sqref="A20:N28">
-    <cfRule type="expression" dxfId="6" priority="2">
+  <conditionalFormatting sqref="A20:N29">
+    <cfRule type="expression" dxfId="5" priority="1">
       <formula>$E20=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A29:N29">
-    <cfRule type="expression" dxfId="5" priority="1">
-      <formula>$E29=0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -18060,17 +18069,17 @@
   <sheetData>
     <row r="1" spans="1:14" ht="19.5" customHeight="1">
       <c r="A1" s="17" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="16.5" customHeight="1">
       <c r="A2" s="18" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="16.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="16.5" customHeight="1">
@@ -18203,7 +18212,7 @@
         <v>1</v>
       </c>
       <c r="B15" s="39" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C15" s="40" t="s">
         <v>273</v>
@@ -18229,13 +18238,13 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="J15" s="39" t="s">
+        <v>450</v>
+      </c>
+      <c r="K15" s="39" t="s">
         <v>451</v>
       </c>
-      <c r="K15" s="39" t="s">
+      <c r="L15" s="39" t="s">
         <v>452</v>
-      </c>
-      <c r="L15" s="39" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="16.5" customHeight="1">
@@ -18243,7 +18252,7 @@
         <v>2</v>
       </c>
       <c r="B16" s="39" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C16" s="40" t="s">
         <v>273</v>
@@ -18269,13 +18278,13 @@
         <v>7.2</v>
       </c>
       <c r="J16" s="39" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="K16" s="39" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="L16" s="39" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="16.5" customHeight="1">
@@ -18283,7 +18292,7 @@
         <v>3</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C17" s="20" t="s">
         <v>324</v>
@@ -18311,10 +18320,10 @@
         <v>333</v>
       </c>
       <c r="K17" s="21" t="s">
+        <v>456</v>
+      </c>
+      <c r="L17" s="21" t="s">
         <v>457</v>
-      </c>
-      <c r="L17" s="21" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="16.5" customHeight="1">
@@ -18322,7 +18331,7 @@
         <v>4</v>
       </c>
       <c r="B18" s="21" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C18" s="20" t="s">
         <v>333</v>
@@ -18350,10 +18359,10 @@
         <v>319</v>
       </c>
       <c r="K18" s="21" t="s">
+        <v>459</v>
+      </c>
+      <c r="L18" s="21" t="s">
         <v>460</v>
-      </c>
-      <c r="L18" s="21" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="16.5" customHeight="1">
@@ -18361,7 +18370,7 @@
         <v>5</v>
       </c>
       <c r="B19" s="21" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C19" s="20" t="s">
         <v>333</v>
@@ -18387,10 +18396,10 @@
       </c>
       <c r="J19" s="21"/>
       <c r="K19" s="21" t="s">
+        <v>462</v>
+      </c>
+      <c r="L19" s="21" t="s">
         <v>463</v>
-      </c>
-      <c r="L19" s="21" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="16.5" customHeight="1">
@@ -18398,7 +18407,7 @@
         <v>6</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C20" s="20" t="s">
         <v>318</v>
@@ -18424,10 +18433,10 @@
       </c>
       <c r="J20" s="21"/>
       <c r="K20" s="21" t="s">
+        <v>465</v>
+      </c>
+      <c r="L20" s="21" t="s">
         <v>466</v>
-      </c>
-      <c r="L20" s="21" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="16.5" customHeight="1">
@@ -18464,10 +18473,10 @@
         <v>324</v>
       </c>
       <c r="K21" s="21" t="s">
+        <v>467</v>
+      </c>
+      <c r="L21" s="21" t="s">
         <v>468</v>
-      </c>
-      <c r="L21" s="21" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="16.5" customHeight="1">
@@ -18501,10 +18510,10 @@
       </c>
       <c r="J22" s="21"/>
       <c r="K22" s="21" t="s">
+        <v>469</v>
+      </c>
+      <c r="L22" s="21" t="s">
         <v>470</v>
-      </c>
-      <c r="L22" s="21" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="16.5" customHeight="1">

--- a/운동프로그램_10일주기_v19.xlsx
+++ b/운동프로그램_10일주기_v19.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b2bc197408547891/Desktop/운동/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="365" documentId="11_56CBE09B577CB57806506320C7833877887CCA2D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FBB702CC-B404-4F9F-A783-3AD67C5F0800}"/>
+  <xr:revisionPtr revIDLastSave="368" documentId="11_56CBE09B577CB57806506320C7833877887CCA2D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F430E9A-0B19-4A13-B70B-E851EBFE5A29}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="883" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2204" uniqueCount="1136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2205" uniqueCount="1137">
   <si>
     <t>9일차 — 어깨·팔 B</t>
   </si>
@@ -3497,6 +3497,9 @@
   <si>
     <t>· [2026-09-05] 1일차 랫풀다운 4 → 양팔 2 + 원암 랫풀다운 2, 6일차 시티드 케이블 로우 5 → 양팔 3 + 원암 케이블 로우 2 — 사용자 요청. 원암은 좌우 한 번씩을 1세트로 세고 수행 시간만 두 배(80초)라 세트 241 불변, 광배 직접 13 그대로, 1일차 70→72분 · 6일차 71→72분. 계수맵에 원암 2종을 신설(D핸들 뉴트럴 → 이두 0.33, 원암 로우 → 승모 중부 0.5) — 이두 간접 +0.3. 시작 무게는 양팔의 절반(20)이고 약한 쪽 기준으로 올린다.</t>
     <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>[2026-09-05] 6일차를 하루 미룸 — 늦게 일어나 갔더니 헬스장이 닫혀 있었다. 실제 1일차는 08-31이었으나 앱 달력 기준을 09-01로 당겨 적어 09-06이 6일차가 되게 했다(이 사이클만 11일, 다음 사이클 1일차 09-11).</t>
   </si>
 </sst>
 </file>
@@ -9145,7 +9148,7 @@
         <v>133</v>
       </c>
       <c r="B14" s="84">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="C14" s="16">
         <f t="shared" si="0"/>
@@ -9167,7 +9170,9 @@
         <v>25</v>
       </c>
       <c r="J14" s="4"/>
-      <c r="K14" s="65"/>
+      <c r="K14" s="65" t="s">
+        <v>1136</v>
+      </c>
       <c r="L14" s="103"/>
       <c r="M14" s="103"/>
     </row>
